--- a/summary_results.xlsx
+++ b/summary_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\benchmark_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAE1F78-8C87-4787-AC31-63D5CA718ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDB844F-AC04-4F60-9067-E7FD9DEB4089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>d</t>
   </si>
   <si>
-    <t>best-known obj</t>
-  </si>
-  <si>
     <t>best found obj</t>
   </si>
   <si>
@@ -1196,6 +1193,9 @@
   </si>
   <si>
     <t>Summary (MDP/Team_formation/StackOverflow)</t>
+  </si>
+  <si>
+    <t>best-known/reference obj</t>
   </si>
 </sst>
 </file>
@@ -2116,19 +2116,19 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G1" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L1" s="15"/>
       <c r="M1" s="15"/>
       <c r="N1" s="15"/>
       <c r="O1" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P1" s="16"/>
       <c r="Q1" s="16"/>
@@ -2151,51 +2151,51 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>391</v>
       </c>
       <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" t="s">
         <v>337</v>
       </c>
-      <c r="L2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
+        <v>336</v>
+      </c>
+      <c r="P2" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R2" t="s">
         <v>8</v>
-      </c>
-      <c r="N2" t="s">
-        <v>338</v>
-      </c>
-      <c r="O2" t="s">
-        <v>337</v>
-      </c>
-      <c r="P2" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>15606</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>13992</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>28924</v>
@@ -2304,7 +2304,7 @@
         <v>6407</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>10240</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>16840</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>11143</v>
@@ -2436,7 +2436,7 @@
         <v>260.60000000000002</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>16386</v>
@@ -2480,7 +2480,7 @@
         <v>483.6</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2501,15 +2501,15 @@
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
       <c r="K10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>18772</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C12">
         <v>23133</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C13">
         <v>5241</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C14">
         <v>12006</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C15">
         <v>9875</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>1133</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>198</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -3039,7 +3039,7 @@
         <v>800</v>
       </c>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>800</v>
       </c>
       <c r="M21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>800</v>
       </c>
       <c r="Q21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22">
         <v>400</v>
@@ -3095,7 +3095,7 @@
         <v>1026</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>1026</v>
       </c>
       <c r="M22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>1026</v>
       </c>
       <c r="Q22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <v>800</v>
@@ -3151,7 +3151,7 @@
         <v>544</v>
       </c>
       <c r="I23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>544</v>
       </c>
       <c r="M23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3175,7 +3175,7 @@
         <v>544</v>
       </c>
       <c r="Q23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>800</v>
@@ -3207,7 +3207,7 @@
         <v>634</v>
       </c>
       <c r="I24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>634</v>
       </c>
       <c r="M24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>633.6</v>
       </c>
       <c r="Q24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25">
         <v>1000</v>
@@ -3287,7 +3287,7 @@
         <v>4554</v>
       </c>
       <c r="Q25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26">
         <v>125</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27">
         <v>2000</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>2000</v>
@@ -3431,7 +3431,7 @@
         <v>6314</v>
       </c>
       <c r="I28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>6316</v>
       </c>
       <c r="M28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>6311.2</v>
       </c>
       <c r="Q28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29">
         <v>250</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30">
         <v>4000</v>
@@ -3543,7 +3543,7 @@
         <v>303.2</v>
       </c>
       <c r="I30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>304</v>
       </c>
       <c r="Q30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <v>500</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32">
         <v>1000</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33">
         <v>500</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>400</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37">
         <v>400</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <v>400</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39">
         <v>1024</v>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40">
         <v>256</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41">
         <v>171</v>
@@ -4191,10 +4191,10 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42">
         <v>776</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43">
         <v>3361</v>
@@ -4295,7 +4295,7 @@
         <v>3416</v>
       </c>
       <c r="Q43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44">
         <v>378</v>
@@ -4327,7 +4327,7 @@
         <v>15746.4</v>
       </c>
       <c r="I44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45">
         <v>1035</v>
@@ -4383,7 +4383,7 @@
         <v>118659.2</v>
       </c>
       <c r="I45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         <v>118665.2</v>
       </c>
       <c r="M45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -4407,7 +4407,7 @@
         <v>118657.2</v>
       </c>
       <c r="Q45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -4415,10 +4415,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <v>3321</v>
@@ -4439,7 +4439,7 @@
         <v>1208860.8</v>
       </c>
       <c r="I46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>1208863.2</v>
       </c>
       <c r="M46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>1208860.3999999999</v>
       </c>
       <c r="Q46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -4471,10 +4471,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47">
         <v>1500</v>
@@ -4527,10 +4527,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48">
         <v>1500</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49">
         <v>1500</v>
@@ -4639,10 +4639,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50">
         <v>300</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51">
         <v>300</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52">
         <v>300</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53">
         <v>700</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54">
         <v>700</v>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55">
         <v>700</v>
@@ -4975,7 +4975,7 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -4991,7 +4991,7 @@
         <v>2.5739789420904085E-3</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J56" s="8">
         <f>SUM(J19:J55)</f>
@@ -5006,7 +5006,7 @@
         <v>2.3605553781793618E-3</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N56" s="8">
         <f>SUM(N19:N55)</f>
@@ -5021,7 +5021,7 @@
         <v>2.7633878534528387E-3</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R56" s="8">
         <f>SUM(R19:R55)</f>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57">
         <v>4000</v>
@@ -5054,7 +5054,7 @@
         <v>9496.4</v>
       </c>
       <c r="I57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -5066,7 +5066,7 @@
         <v>9498</v>
       </c>
       <c r="M57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>9493.6</v>
       </c>
       <c r="Q57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C58">
         <v>450</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C59">
         <v>450</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60">
         <v>450</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C61">
         <v>450</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62">
         <v>450</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63">
         <v>595</v>
@@ -5414,7 +5414,7 @@
         <v>1187.5999999999999</v>
       </c>
       <c r="Q63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C64">
         <v>595</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C65">
         <v>595</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C66">
         <v>595</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67">
         <v>595</v>
@@ -5646,10 +5646,10 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68">
         <v>760</v>
@@ -5694,7 +5694,7 @@
         <v>1558</v>
       </c>
       <c r="Q68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C69">
         <v>760</v>
@@ -5726,7 +5726,7 @@
         <v>1558</v>
       </c>
       <c r="I69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>1556.8</v>
       </c>
       <c r="Q69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C70">
         <v>760</v>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71">
         <v>760</v>
@@ -5838,7 +5838,7 @@
         <v>1558</v>
       </c>
       <c r="I71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C72">
         <v>760</v>
@@ -5918,7 +5918,7 @@
         <v>1557.2</v>
       </c>
       <c r="Q72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73">
         <v>945</v>
@@ -5974,7 +5974,7 @@
         <v>1976.8</v>
       </c>
       <c r="Q73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>945</v>
@@ -6030,7 +6030,7 @@
         <v>1976.8</v>
       </c>
       <c r="Q74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75">
         <v>945</v>
@@ -6062,7 +6062,7 @@
         <v>1977.2</v>
       </c>
       <c r="I75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -6086,7 +6086,7 @@
         <v>1976</v>
       </c>
       <c r="Q75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C76">
         <v>945</v>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77">
         <v>945</v>
@@ -6198,7 +6198,7 @@
         <v>1976.4</v>
       </c>
       <c r="Q77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78">
         <v>1150</v>
@@ -6230,7 +6230,7 @@
         <v>2446.4</v>
       </c>
       <c r="I78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>2445.1999999999998</v>
       </c>
       <c r="Q78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -6262,10 +6262,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79">
         <v>1150</v>
@@ -6286,7 +6286,7 @@
         <v>2446.8000000000002</v>
       </c>
       <c r="I79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>2448</v>
       </c>
       <c r="M79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -6310,7 +6310,7 @@
         <v>2445.1999999999998</v>
       </c>
       <c r="Q79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80">
         <v>1150</v>
@@ -6342,7 +6342,7 @@
         <v>2447.1999999999998</v>
       </c>
       <c r="I80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -6354,7 +6354,7 @@
         <v>2448</v>
       </c>
       <c r="M80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>2446</v>
       </c>
       <c r="Q80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -6374,10 +6374,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81">
         <v>1150</v>
@@ -6398,7 +6398,7 @@
         <v>2447.1999999999998</v>
       </c>
       <c r="I81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -6422,7 +6422,7 @@
         <v>2445.6</v>
       </c>
       <c r="Q81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -6430,10 +6430,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82">
         <v>1150</v>
@@ -6478,7 +6478,7 @@
         <v>2445.6</v>
       </c>
       <c r="Q82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83">
         <v>1272</v>
@@ -6510,7 +6510,7 @@
         <v>2752.4</v>
       </c>
       <c r="I83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -6522,7 +6522,7 @@
         <v>2753.6</v>
       </c>
       <c r="M83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>2749.6</v>
       </c>
       <c r="Q83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84">
         <v>1272</v>
@@ -6566,7 +6566,7 @@
         <v>2752.4</v>
       </c>
       <c r="I84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>2754</v>
       </c>
       <c r="M84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N84">
         <v>0</v>
@@ -6590,7 +6590,7 @@
         <v>2750.8</v>
       </c>
       <c r="Q84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85">
         <v>1272</v>
@@ -6622,7 +6622,7 @@
         <v>2752</v>
       </c>
       <c r="I85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -6634,7 +6634,7 @@
         <v>2754</v>
       </c>
       <c r="M85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N85">
         <v>0</v>
@@ -6646,7 +6646,7 @@
         <v>2750</v>
       </c>
       <c r="Q85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86">
         <v>1272</v>
@@ -6678,7 +6678,7 @@
         <v>2752.4</v>
       </c>
       <c r="I86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -6702,7 +6702,7 @@
         <v>2750.8</v>
       </c>
       <c r="Q86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87">
         <v>1272</v>
@@ -6734,7 +6734,7 @@
         <v>2752</v>
       </c>
       <c r="I87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>2750.4</v>
       </c>
       <c r="Q87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -6766,10 +6766,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88">
         <v>1534</v>
@@ -6790,7 +6790,7 @@
         <v>3417.2</v>
       </c>
       <c r="I88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -6802,7 +6802,7 @@
         <v>3419.2</v>
       </c>
       <c r="M88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N88">
         <v>0</v>
@@ -6814,7 +6814,7 @@
         <v>3415.6</v>
       </c>
       <c r="Q88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89">
         <v>1534</v>
@@ -6846,7 +6846,7 @@
         <v>3417.6</v>
       </c>
       <c r="I89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>3418.8</v>
       </c>
       <c r="M89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>3415.2</v>
       </c>
       <c r="Q89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -6878,10 +6878,10 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90">
         <v>1534</v>
@@ -6902,7 +6902,7 @@
         <v>3418</v>
       </c>
       <c r="I90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -6914,7 +6914,7 @@
         <v>3418.8</v>
       </c>
       <c r="M90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N90">
         <v>0</v>
@@ -6926,7 +6926,7 @@
         <v>3415.6</v>
       </c>
       <c r="Q90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>1534</v>
@@ -6958,7 +6958,7 @@
         <v>3417.6</v>
       </c>
       <c r="I91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>3419.2</v>
       </c>
       <c r="M91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>3414.8</v>
       </c>
       <c r="Q91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C92">
         <v>1534</v>
@@ -7038,7 +7038,7 @@
         <v>3416</v>
       </c>
       <c r="Q92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -7062,7 +7062,7 @@
         <v>8.0753414458432959E-4</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J93" s="8">
         <f>SUM(J57:J92)</f>
@@ -7077,7 +7077,7 @@
         <v>3.6506078228246711E-4</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N93" s="8">
         <f>SUM(N57:N92)</f>
@@ -7092,7 +7092,7 @@
         <v>1.5143965976658306E-3</v>
       </c>
       <c r="Q93" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R93" s="8">
         <f>SUM(R57:R92)</f>
@@ -7101,10 +7101,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B94" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C94">
         <v>2500</v>
@@ -7125,7 +7125,7 @@
         <v>1152822.3999999999</v>
       </c>
       <c r="I94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B95" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C95">
         <v>2500</v>
@@ -7181,7 +7181,7 @@
         <v>1153691.2</v>
       </c>
       <c r="I95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B96" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C96">
         <v>2500</v>
@@ -7237,7 +7237,7 @@
         <v>1128895.6000000001</v>
       </c>
       <c r="I96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -7269,10 +7269,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B97" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C97">
         <v>2500</v>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C98">
         <v>2500</v>
@@ -7349,7 +7349,7 @@
         <v>1147367.2</v>
       </c>
       <c r="I98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -7361,7 +7361,7 @@
         <v>1147840</v>
       </c>
       <c r="M98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N98">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         <v>1147769.2</v>
       </c>
       <c r="Q98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -7381,10 +7381,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B99" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C99">
         <v>2500</v>
@@ -7437,10 +7437,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B100" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C100">
         <v>2500</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B101" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C101">
         <v>2500</v>
@@ -7517,7 +7517,7 @@
         <v>1148724.3999999999</v>
       </c>
       <c r="I101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B102" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C102">
         <v>2500</v>
@@ -7573,7 +7573,7 @@
         <v>1142543.2</v>
       </c>
       <c r="I102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B103" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C103">
         <v>2500</v>
@@ -7629,7 +7629,7 @@
         <v>1138607.6000000001</v>
       </c>
       <c r="I103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -7677,7 +7677,7 @@
         <v>2.3037513103146826E-4</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J104" s="8">
         <f>SUM(J94:J103)</f>
@@ -7692,7 +7692,7 @@
         <v>1.4982421786531849E-5</v>
       </c>
       <c r="M104" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N104" s="8">
         <f>SUM(N94:N103)</f>
@@ -7707,7 +7707,7 @@
         <v>3.9814304228935367E-5</v>
       </c>
       <c r="Q104" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R104" s="8">
         <f>SUM(R94:R103)</f>
@@ -7716,10 +7716,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C105">
         <v>500</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C106">
         <v>500</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B107" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C107">
         <v>500</v>
@@ -7884,10 +7884,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C108">
         <v>500</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C109">
         <v>500</v>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C110">
         <v>500</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C111">
         <v>500</v>
@@ -8108,10 +8108,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C112">
         <v>500</v>
@@ -8164,10 +8164,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C113">
         <v>500</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C114">
         <v>500</v>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C115">
         <v>500</v>
@@ -8332,10 +8332,10 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B116" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C116">
         <v>500</v>
@@ -8388,10 +8388,10 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B117" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C117">
         <v>500</v>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C118">
         <v>500</v>
@@ -8500,10 +8500,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C119">
         <v>500</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B120" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C120">
         <v>500</v>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C121">
         <v>500</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C122">
         <v>500</v>
@@ -8724,10 +8724,10 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C123">
         <v>500</v>
@@ -8780,10 +8780,10 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C124">
         <v>500</v>
@@ -8836,7 +8836,7 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B125" s="8"/>
       <c r="C125" s="8">
@@ -8890,10 +8890,10 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B126" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C126">
         <v>2000</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C127">
         <v>2000</v>
@@ -9002,10 +9002,10 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B128" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C128">
         <v>2000</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C129">
         <v>2000</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B130" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C130">
         <v>2000</v>
@@ -9170,10 +9170,10 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B131" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C131">
         <v>3000</v>
@@ -9226,10 +9226,10 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B132" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C132">
         <v>3000</v>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C133">
         <v>3000</v>
@@ -9338,10 +9338,10 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B134" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C134">
         <v>3000</v>
@@ -9394,10 +9394,10 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C135">
         <v>3000</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C136">
         <v>5000</v>
@@ -9506,10 +9506,10 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B137" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C137">
         <v>5000</v>
@@ -9562,10 +9562,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B138" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C138">
         <v>5000</v>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B139" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C139">
         <v>5000</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C140">
         <v>5000</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B141" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C141">
         <v>6000</v>
@@ -9786,10 +9786,10 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B142" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C142">
         <v>6000</v>
@@ -9842,10 +9842,10 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B143" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C143">
         <v>6000</v>
@@ -9898,10 +9898,10 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B144" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C144">
         <v>6000</v>
@@ -9954,10 +9954,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B145" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C145">
         <v>6000</v>
@@ -10010,11 +10010,11 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B146" s="8"/>
       <c r="C146" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="9"/>
@@ -10064,10 +10064,10 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C147">
         <v>2000</v>
@@ -10120,10 +10120,10 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B148" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C148">
         <v>2000</v>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B149" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C149">
         <v>2000</v>
@@ -10232,10 +10232,10 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B150" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C150">
         <v>2000</v>
@@ -10288,10 +10288,10 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B151" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C151">
         <v>2000</v>
@@ -10344,10 +10344,10 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B152" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C152">
         <v>2000</v>
@@ -10400,10 +10400,10 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B153" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C153">
         <v>2000</v>
@@ -10456,10 +10456,10 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C154">
         <v>2000</v>
@@ -10512,10 +10512,10 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B155" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C155">
         <v>2000</v>
@@ -10568,10 +10568,10 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B156" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C156">
         <v>2000</v>
@@ -10624,10 +10624,10 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B157" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C157">
         <v>2000</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C158">
         <v>2000</v>
@@ -10736,10 +10736,10 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B159" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C159">
         <v>2000</v>
@@ -10792,10 +10792,10 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B160" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C160">
         <v>2000</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C161">
         <v>2000</v>
@@ -10904,10 +10904,10 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B162" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C162">
         <v>2000</v>
@@ -10960,10 +10960,10 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B163" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C163">
         <v>2000</v>
@@ -11016,10 +11016,10 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B164" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C164">
         <v>2000</v>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B165" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C165">
         <v>2000</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B166" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C166">
         <v>2000</v>
@@ -11184,7 +11184,7 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B167" s="8"/>
       <c r="C167" s="8">
@@ -11202,7 +11202,7 @@
         <v>7.4684162328189809E-5</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J167" s="8">
         <f>SUM(J147:J166)</f>
@@ -11217,7 +11217,7 @@
         <v>1.7529559218978344E-7</v>
       </c>
       <c r="M167" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N167" s="8">
         <f>SUM(N147:N166)</f>
@@ -11232,7 +11232,7 @@
         <v>2.8026728780104248E-6</v>
       </c>
       <c r="Q167" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R167" s="8">
         <f>SUM(R147:R166)</f>
@@ -11241,10 +11241,10 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B168" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C168">
         <v>500</v>
@@ -11297,10 +11297,10 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B169" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C169">
         <v>500</v>
@@ -11353,10 +11353,10 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B170" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C170">
         <v>500</v>
@@ -11409,10 +11409,10 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B171" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C171">
         <v>500</v>
@@ -11465,10 +11465,10 @@
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B172" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C172">
         <v>500</v>
@@ -11521,10 +11521,10 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B173" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C173">
         <v>500</v>
@@ -11577,10 +11577,10 @@
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C174">
         <v>500</v>
@@ -11633,10 +11633,10 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C175">
         <v>500</v>
@@ -11689,10 +11689,10 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C176">
         <v>500</v>
@@ -11745,10 +11745,10 @@
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C177">
         <v>500</v>
@@ -11801,10 +11801,10 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B178" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C178">
         <v>500</v>
@@ -11857,10 +11857,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B179" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C179">
         <v>500</v>
@@ -11913,10 +11913,10 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B180" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C180">
         <v>500</v>
@@ -11969,10 +11969,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B181" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C181">
         <v>500</v>
@@ -12025,10 +12025,10 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C182">
         <v>500</v>
@@ -12081,10 +12081,10 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B183" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C183">
         <v>500</v>
@@ -12137,10 +12137,10 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B184" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C184">
         <v>500</v>
@@ -12193,10 +12193,10 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B185" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C185">
         <v>500</v>
@@ -12249,10 +12249,10 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B186" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C186">
         <v>500</v>
@@ -12305,10 +12305,10 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B187" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C187">
         <v>500</v>
@@ -12361,7 +12361,7 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="8">
@@ -12415,10 +12415,10 @@
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C189">
         <v>2000</v>
@@ -12471,10 +12471,10 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C190">
         <v>2000</v>
@@ -12527,10 +12527,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C191">
         <v>2000</v>
@@ -12583,10 +12583,10 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B192" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C192">
         <v>2000</v>
@@ -12639,10 +12639,10 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B193" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C193">
         <v>2000</v>
@@ -12695,10 +12695,10 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B194" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C194">
         <v>2000</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B195" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C195">
         <v>2000</v>
@@ -12807,10 +12807,10 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B196" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C196">
         <v>2000</v>
@@ -12831,7 +12831,7 @@
         <v>11282639.256440001</v>
       </c>
       <c r="I196" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -12863,10 +12863,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B197" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C197">
         <v>2000</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B198" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C198">
         <v>2000</v>
@@ -12975,10 +12975,10 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B199" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C199">
         <v>2000</v>
@@ -13031,10 +13031,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B200" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C200">
         <v>2000</v>
@@ -13055,7 +13055,7 @@
         <v>11283465.4152903</v>
       </c>
       <c r="I200" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B201" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C201">
         <v>2000</v>
@@ -13143,10 +13143,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B202" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C202">
         <v>2000</v>
@@ -13167,7 +13167,7 @@
         <v>11288472.947700299</v>
       </c>
       <c r="I202" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -13199,10 +13199,10 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B203" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C203">
         <v>2000</v>
@@ -13255,10 +13255,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B204" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C204">
         <v>2000</v>
@@ -13311,10 +13311,10 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C205">
         <v>2000</v>
@@ -13335,7 +13335,7 @@
         <v>11294209.747011101</v>
       </c>
       <c r="I205" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -13367,10 +13367,10 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B206" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C206">
         <v>2000</v>
@@ -13423,10 +13423,10 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B207" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C207">
         <v>2000</v>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B208" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C208">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8">
@@ -13553,7 +13553,7 @@
         <v>6.8271909033567669E-5</v>
       </c>
       <c r="I209" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J209" s="8">
         <f>SUM(J189:J208)</f>
@@ -13566,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="M209" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N209" s="8">
         <f>SUM(N189:N208)</f>
@@ -13580,7 +13580,7 @@
         <v>3.757193501832543E-6</v>
       </c>
       <c r="Q209" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R209" s="8">
         <f>SUM(R189:R208)</f>
@@ -13589,10 +13589,10 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B210" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C210">
         <v>500</v>
@@ -13645,10 +13645,10 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B211" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C211">
         <v>500</v>
@@ -13701,10 +13701,10 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B212" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C212">
         <v>500</v>
@@ -13757,10 +13757,10 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B213" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C213">
         <v>500</v>
@@ -13813,10 +13813,10 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B214" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C214">
         <v>500</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B215" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C215">
         <v>500</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B216" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C216">
         <v>500</v>
@@ -13981,10 +13981,10 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B217" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C217">
         <v>500</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B218" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C218">
         <v>500</v>
@@ -14093,10 +14093,10 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B219" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C219">
         <v>500</v>
@@ -14149,10 +14149,10 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B220" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C220">
         <v>500</v>
@@ -14205,10 +14205,10 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B221" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C221">
         <v>500</v>
@@ -14261,10 +14261,10 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B222" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C222">
         <v>500</v>
@@ -14317,10 +14317,10 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C223">
         <v>500</v>
@@ -14373,10 +14373,10 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C224">
         <v>500</v>
@@ -14429,10 +14429,10 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B225" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C225">
         <v>500</v>
@@ -14485,10 +14485,10 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B226" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C226">
         <v>500</v>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B227" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C227">
         <v>500</v>
@@ -14597,10 +14597,10 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B228" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C228">
         <v>500</v>
@@ -14653,10 +14653,10 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B229" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C229">
         <v>500</v>
@@ -14709,7 +14709,7 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8">
@@ -14763,10 +14763,10 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B231" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C231">
         <v>3000</v>
@@ -14787,7 +14787,7 @@
         <v>43461617.200000003</v>
       </c>
       <c r="I231" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -14799,7 +14799,7 @@
         <v>43465561</v>
       </c>
       <c r="M231" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N231">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>43465282.799999997</v>
       </c>
       <c r="Q231" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -14819,10 +14819,10 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B232" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C232">
         <v>3000</v>
@@ -14843,7 +14843,7 @@
         <v>67012027.399999902</v>
       </c>
       <c r="I232" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>67019102.799999997</v>
       </c>
       <c r="Q232" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R232">
         <v>0</v>
@@ -14875,10 +14875,10 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B233" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C233">
         <v>3000</v>
@@ -14899,7 +14899,7 @@
         <v>66999458</v>
       </c>
       <c r="I233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -14911,7 +14911,7 @@
         <v>67014170</v>
       </c>
       <c r="M233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N233">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>67001704</v>
       </c>
       <c r="Q233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R233">
         <v>0</v>
@@ -14931,10 +14931,10 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B234" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C234">
         <v>3000</v>
@@ -14987,10 +14987,10 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B235" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C235">
         <v>3000</v>
@@ -15035,7 +15035,7 @@
         <v>67023660.799999997</v>
       </c>
       <c r="Q235" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R235">
         <v>0</v>
@@ -15043,10 +15043,10 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B236" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C236">
         <v>3000</v>
@@ -15067,7 +15067,7 @@
         <v>67050241.600000001</v>
       </c>
       <c r="I236" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -15099,10 +15099,10 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B237" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C237">
         <v>3000</v>
@@ -15155,10 +15155,10 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B238" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C238">
         <v>3000</v>
@@ -15179,7 +15179,7 @@
         <v>95555581.400000006</v>
       </c>
       <c r="I238" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J238">
         <v>0</v>
@@ -15191,7 +15191,7 @@
         <v>95571113</v>
       </c>
       <c r="M238" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N238">
         <v>0</v>
@@ -15203,7 +15203,7 @@
         <v>95565209.400000006</v>
       </c>
       <c r="Q238" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R238">
         <v>0</v>
@@ -15211,10 +15211,10 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B239" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C239">
         <v>3000</v>
@@ -15235,7 +15235,7 @@
         <v>95521123.599999905</v>
       </c>
       <c r="I239" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J239">
         <v>0</v>
@@ -15247,7 +15247,7 @@
         <v>95528844.400000006</v>
       </c>
       <c r="M239" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N239">
         <v>0</v>
@@ -15259,7 +15259,7 @@
         <v>95529236.400000006</v>
       </c>
       <c r="Q239" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R239">
         <v>0</v>
@@ -15267,10 +15267,10 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B240" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C240">
         <v>3000</v>
@@ -15291,7 +15291,7 @@
         <v>95591579.200000003</v>
       </c>
       <c r="I240" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J240">
         <v>0</v>
@@ -15303,7 +15303,7 @@
         <v>95599014.799999893</v>
       </c>
       <c r="M240" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N240">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>95591913.799999997</v>
       </c>
       <c r="Q240" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R240">
         <v>0</v>
@@ -15323,10 +15323,10 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B241" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C241">
         <v>3000</v>
@@ -15347,7 +15347,7 @@
         <v>24919861</v>
       </c>
       <c r="I241" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -15379,10 +15379,10 @@
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B242" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C242">
         <v>3000</v>
@@ -15403,7 +15403,7 @@
         <v>95569212.400000006</v>
       </c>
       <c r="I242" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J242">
         <v>0</v>
@@ -15415,7 +15415,7 @@
         <v>95584482</v>
       </c>
       <c r="M242" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N242">
         <v>0</v>
@@ -15427,7 +15427,7 @@
         <v>95582758.799999997</v>
       </c>
       <c r="Q242" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R242">
         <v>0</v>
@@ -15435,10 +15435,10 @@
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B243" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C243">
         <v>3000</v>
@@ -15459,7 +15459,7 @@
         <v>24900661.600000001</v>
       </c>
       <c r="I243" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -15471,7 +15471,7 @@
         <v>24911029.800000001</v>
       </c>
       <c r="M243" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N243">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         <v>24910869.199999999</v>
       </c>
       <c r="Q243" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R243">
         <v>0</v>
@@ -15491,10 +15491,10 @@
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B244" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C244">
         <v>3000</v>
@@ -15515,7 +15515,7 @@
         <v>24890456.600000001</v>
       </c>
       <c r="I244" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -15547,10 +15547,10 @@
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B245" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C245">
         <v>3000</v>
@@ -15571,7 +15571,7 @@
         <v>24902546.600000001</v>
       </c>
       <c r="I245" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -15595,7 +15595,7 @@
         <v>24904629.399999999</v>
       </c>
       <c r="Q245" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R245">
         <v>0</v>
@@ -15603,10 +15603,10 @@
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B246" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C246">
         <v>3000</v>
@@ -15627,7 +15627,7 @@
         <v>24890069</v>
       </c>
       <c r="I246" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -15639,7 +15639,7 @@
         <v>24895005.399999902</v>
       </c>
       <c r="M246" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N246">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>24894394</v>
       </c>
       <c r="Q246" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R246">
         <v>0</v>
@@ -15659,10 +15659,10 @@
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B247" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C247">
         <v>3000</v>
@@ -15683,7 +15683,7 @@
         <v>43436259.600000001</v>
       </c>
       <c r="I247" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -15695,7 +15695,7 @@
         <v>43444264</v>
       </c>
       <c r="M247" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N247">
         <v>0</v>
@@ -15707,7 +15707,7 @@
         <v>43438890</v>
       </c>
       <c r="Q247" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R247">
         <v>0</v>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B248" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C248">
         <v>3000</v>
@@ -15739,7 +15739,7 @@
         <v>43468569.399999902</v>
       </c>
       <c r="I248" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -15771,10 +15771,10 @@
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B249" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C249">
         <v>3000</v>
@@ -15795,7 +15795,7 @@
         <v>43456187</v>
       </c>
       <c r="I249" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -15827,10 +15827,10 @@
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B250" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C250">
         <v>3000</v>
@@ -15851,7 +15851,7 @@
         <v>43444839.600000001</v>
       </c>
       <c r="I250" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -15883,7 +15883,7 @@
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8">
@@ -15901,7 +15901,7 @@
         <v>3.9132569547953012E-4</v>
       </c>
       <c r="I251" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J251" s="8">
         <f>SUM(J231:J250)</f>
@@ -15916,7 +15916,7 @@
         <v>2.1204684058721482E-4</v>
       </c>
       <c r="M251" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N251" s="8">
         <f>SUM(N231:N250)</f>
@@ -15931,7 +15931,7 @@
         <v>2.5666646118477539E-4</v>
       </c>
       <c r="Q251" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R251" s="8">
         <f>SUM(R231:R250)</f>
@@ -15940,10 +15940,10 @@
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B252" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C252">
         <v>3000</v>
@@ -15964,7 +15964,7 @@
         <v>6502041.2000000002</v>
       </c>
       <c r="I252" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -15996,10 +15996,10 @@
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C253">
         <v>3000</v>
@@ -16052,10 +16052,10 @@
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B254" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C254">
         <v>3000</v>
@@ -16076,7 +16076,7 @@
         <v>29866613.199999899</v>
       </c>
       <c r="I254" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -16108,10 +16108,10 @@
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B255" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C255">
         <v>3000</v>
@@ -16164,10 +16164,10 @@
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B256" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C256">
         <v>3000</v>
@@ -16220,10 +16220,10 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B257" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C257">
         <v>5000</v>
@@ -16244,7 +16244,7 @@
         <v>17508171.600000001</v>
       </c>
       <c r="I257" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J257">
         <v>0</v>
@@ -16256,7 +16256,7 @@
         <v>17508889.600000001</v>
       </c>
       <c r="M257" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N257">
         <v>0</v>
@@ -16268,7 +16268,7 @@
         <v>17508731.600000001</v>
       </c>
       <c r="Q257" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R257">
         <v>0</v>
@@ -16276,10 +16276,10 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B258" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C258">
         <v>5000</v>
@@ -16300,7 +16300,7 @@
         <v>50101554.200000003</v>
       </c>
       <c r="I258" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J258">
         <v>0</v>
@@ -16312,7 +16312,7 @@
         <v>50102738.600000001</v>
       </c>
       <c r="M258" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -16324,7 +16324,7 @@
         <v>50102376.200000003</v>
       </c>
       <c r="Q258" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R258">
         <v>0</v>
@@ -16332,10 +16332,10 @@
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B259" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C259">
         <v>5000</v>
@@ -16356,7 +16356,7 @@
         <v>82035747.200000003</v>
       </c>
       <c r="I259" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>82039521.200000003</v>
       </c>
       <c r="M259" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -16380,7 +16380,7 @@
         <v>82037425.599999994</v>
       </c>
       <c r="Q259" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R259">
         <v>0</v>
@@ -16388,10 +16388,10 @@
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B260" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C260">
         <v>5000</v>
@@ -16412,7 +16412,7 @@
         <v>129411290</v>
       </c>
       <c r="I260" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -16424,7 +16424,7 @@
         <v>129413096.599999</v>
       </c>
       <c r="M260" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -16436,7 +16436,7 @@
         <v>129412464.40000001</v>
       </c>
       <c r="Q260" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R260">
         <v>0</v>
@@ -16444,10 +16444,10 @@
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B261" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C261">
         <v>5000</v>
@@ -16468,7 +16468,7 @@
         <v>160597521</v>
       </c>
       <c r="I261" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -16480,7 +16480,7 @@
         <v>160597826.80000001</v>
       </c>
       <c r="M261" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N261">
         <v>0</v>
@@ -16492,7 +16492,7 @@
         <v>160597582.80000001</v>
       </c>
       <c r="Q261" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R261">
         <v>0</v>
@@ -16500,11 +16500,11 @@
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B262" s="8"/>
       <c r="C262" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D262" s="8"/>
       <c r="E262" s="9"/>
@@ -16518,7 +16518,7 @@
         <v>2.613772174381794E-5</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J262" s="8">
         <f>SUM(J252:J261)</f>
@@ -16533,7 +16533,7 @@
         <v>6.216302791547017E-6</v>
       </c>
       <c r="M262" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N262" s="8">
         <f>SUM(N252:N261)</f>
@@ -16548,7 +16548,7 @@
         <v>1.2033231401112437E-5</v>
       </c>
       <c r="Q262" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R262" s="8">
         <f>SUM(R252:R261)</f>
@@ -16557,10 +16557,10 @@
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B263" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C263">
         <v>300</v>
@@ -16613,10 +16613,10 @@
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B264" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C264">
         <v>300</v>
@@ -16669,10 +16669,10 @@
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B265" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C265">
         <v>300</v>
@@ -16725,10 +16725,10 @@
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B266" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C266">
         <v>400</v>
@@ -16781,10 +16781,10 @@
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B267" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C267">
         <v>400</v>
@@ -16837,10 +16837,10 @@
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B268" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C268">
         <v>400</v>
@@ -16893,10 +16893,10 @@
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B269" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C269">
         <v>400</v>
@@ -16949,10 +16949,10 @@
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B270" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C270">
         <v>500</v>
@@ -17005,10 +17005,10 @@
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B271" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C271">
         <v>500</v>
@@ -17061,10 +17061,10 @@
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B272" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C272">
         <v>500</v>
@@ -17117,10 +17117,10 @@
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B273" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C273">
         <v>100</v>
@@ -17173,10 +17173,10 @@
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B274" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C274">
         <v>500</v>
@@ -17229,10 +17229,10 @@
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B275" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C275">
         <v>100</v>
@@ -17285,10 +17285,10 @@
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B276" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C276">
         <v>100</v>
@@ -17341,10 +17341,10 @@
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B277" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C277">
         <v>100</v>
@@ -17397,10 +17397,10 @@
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B278" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C278">
         <v>200</v>
@@ -17453,10 +17453,10 @@
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B279" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C279">
         <v>200</v>
@@ -17509,10 +17509,10 @@
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B280" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C280">
         <v>200</v>
@@ -17565,10 +17565,10 @@
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B281" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C281">
         <v>200</v>
@@ -17621,10 +17621,10 @@
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B282" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C282">
         <v>300</v>
@@ -17677,11 +17677,11 @@
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D283" s="8"/>
       <c r="E283" s="9"/>
@@ -17731,10 +17731,10 @@
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B284" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C284">
         <v>7000</v>
@@ -17755,7 +17755,7 @@
         <v>142.06044</v>
       </c>
       <c r="I284" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J284">
         <v>0</v>
@@ -17779,7 +17779,7 @@
         <v>109.171176</v>
       </c>
       <c r="Q284" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R284">
         <v>0</v>
@@ -17787,10 +17787,10 @@
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B285" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C285">
         <v>7000</v>
@@ -17811,7 +17811,7 @@
         <v>253.86832000000001</v>
       </c>
       <c r="I285" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -17823,7 +17823,7 @@
         <v>255.52598599999999</v>
       </c>
       <c r="M285" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N285">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>195.100988</v>
       </c>
       <c r="Q285" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R285">
         <v>0</v>
@@ -17843,10 +17843,10 @@
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B286" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C286">
         <v>7000</v>
@@ -17867,7 +17867,7 @@
         <v>352.72425500000003</v>
       </c>
       <c r="I286" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J286">
         <v>0</v>
@@ -17879,7 +17879,7 @@
         <v>354.26472000000001</v>
       </c>
       <c r="M286" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N286">
         <v>0</v>
@@ -17891,7 +17891,7 @@
         <v>247.200424</v>
       </c>
       <c r="Q286" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R286">
         <v>0</v>
@@ -17899,10 +17899,10 @@
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B287" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C287">
         <v>7000</v>
@@ -17923,7 +17923,7 @@
         <v>439.66992399999998</v>
       </c>
       <c r="I287" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J287">
         <v>0</v>
@@ -17935,7 +17935,7 @@
         <v>442.02394700000002</v>
       </c>
       <c r="M287" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N287">
         <v>0</v>
@@ -17947,7 +17947,7 @@
         <v>294.27895599999999</v>
       </c>
       <c r="Q287" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R287">
         <v>0</v>
@@ -17955,10 +17955,10 @@
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B288" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C288">
         <v>7000</v>
@@ -17979,7 +17979,7 @@
         <v>521.21795799999995</v>
       </c>
       <c r="I288" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J288">
         <v>0</v>
@@ -17991,7 +17991,7 @@
         <v>523.14984000000004</v>
       </c>
       <c r="M288" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N288">
         <v>0</v>
@@ -18003,7 +18003,7 @@
         <v>364.401656</v>
       </c>
       <c r="Q288" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R288">
         <v>0</v>
@@ -18011,10 +18011,10 @@
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B289" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C289">
         <v>7000</v>
@@ -18035,7 +18035,7 @@
         <v>141.87070800000001</v>
       </c>
       <c r="I289" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J289">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>92.234967999999995</v>
       </c>
       <c r="Q289" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R289">
         <v>0</v>
@@ -18067,10 +18067,10 @@
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B290" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C290">
         <v>7000</v>
@@ -18091,7 +18091,7 @@
         <v>246.53982199999999</v>
       </c>
       <c r="I290" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J290">
         <v>0</v>
@@ -18115,7 +18115,7 @@
         <v>165.256564</v>
       </c>
       <c r="Q290" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R290">
         <v>0</v>
@@ -18123,10 +18123,10 @@
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B291" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C291">
         <v>7000</v>
@@ -18147,7 +18147,7 @@
         <v>334.37756400000001</v>
       </c>
       <c r="I291" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J291">
         <v>0</v>
@@ -18159,7 +18159,7 @@
         <v>335.78627699999998</v>
       </c>
       <c r="M291" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>220.39002600000001</v>
       </c>
       <c r="Q291" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R291">
         <v>0</v>
@@ -18179,10 +18179,10 @@
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B292" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C292">
         <v>7000</v>
@@ -18203,7 +18203,7 @@
         <v>414.19503700000001</v>
       </c>
       <c r="I292" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J292">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>415.79192899999998</v>
       </c>
       <c r="M292" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N292">
         <v>0</v>
@@ -18227,7 +18227,7 @@
         <v>280.86408399999999</v>
       </c>
       <c r="Q292" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R292">
         <v>0</v>
@@ -18235,10 +18235,10 @@
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B293" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C293">
         <v>7000</v>
@@ -18259,7 +18259,7 @@
         <v>485.52062699999999</v>
       </c>
       <c r="I293" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J293">
         <v>0</v>
@@ -18271,7 +18271,7 @@
         <v>487.507881</v>
       </c>
       <c r="M293" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N293">
         <v>0</v>
@@ -18283,7 +18283,7 @@
         <v>329.18131199999999</v>
       </c>
       <c r="Q293" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R293">
         <v>0</v>
@@ -18291,10 +18291,10 @@
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B294" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C294">
         <v>7000</v>
@@ -18315,7 +18315,7 @@
         <v>160.215506</v>
       </c>
       <c r="I294" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J294">
         <v>0</v>
@@ -18339,7 +18339,7 @@
         <v>125.900102</v>
       </c>
       <c r="Q294" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R294">
         <v>0</v>
@@ -18347,10 +18347,10 @@
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B295" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C295">
         <v>7000</v>
@@ -18371,7 +18371,7 @@
         <v>280.17756600000001</v>
       </c>
       <c r="I295" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J295">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>281.60028</v>
       </c>
       <c r="M295" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N295">
         <v>0</v>
@@ -18395,7 +18395,7 @@
         <v>215.60388599999999</v>
       </c>
       <c r="Q295" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R295">
         <v>0</v>
@@ -18403,10 +18403,10 @@
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C296">
         <v>7000</v>
@@ -18427,7 +18427,7 @@
         <v>387.01029399999999</v>
       </c>
       <c r="I296" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J296">
         <v>0</v>
@@ -18439,7 +18439,7 @@
         <v>387.996374</v>
       </c>
       <c r="M296" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N296">
         <v>0</v>
@@ -18451,7 +18451,7 @@
         <v>278.52568600000001</v>
       </c>
       <c r="Q296" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R296">
         <v>0</v>
@@ -18459,10 +18459,10 @@
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B297" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C297">
         <v>7000</v>
@@ -18483,7 +18483,7 @@
         <v>482.48890399999999</v>
       </c>
       <c r="I297" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J297">
         <v>0</v>
@@ -18495,7 +18495,7 @@
         <v>483.42386800000003</v>
       </c>
       <c r="M297" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N297">
         <v>0</v>
@@ -18507,7 +18507,7 @@
         <v>350.63984399999998</v>
       </c>
       <c r="Q297" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R297">
         <v>0</v>
@@ -18515,10 +18515,10 @@
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B298" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C298">
         <v>7000</v>
@@ -18539,7 +18539,7 @@
         <v>570.37675999999999</v>
       </c>
       <c r="I298" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J298">
         <v>0</v>
@@ -18551,7 +18551,7 @@
         <v>571.93580599999996</v>
       </c>
       <c r="M298" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N298">
         <v>0</v>
@@ -18563,7 +18563,7 @@
         <v>410.54433999999998</v>
       </c>
       <c r="Q298" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R298">
         <v>0</v>
@@ -18571,10 +18571,10 @@
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B299" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C299">
         <v>7000</v>
@@ -18619,7 +18619,7 @@
         <v>110.80799399999999</v>
       </c>
       <c r="Q299" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R299">
         <v>0</v>
@@ -18627,10 +18627,10 @@
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B300" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C300">
         <v>7000</v>
@@ -18651,7 +18651,7 @@
         <v>264.78695800000003</v>
       </c>
       <c r="I300" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -18675,7 +18675,7 @@
         <v>189.78016199999999</v>
       </c>
       <c r="Q300" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R300">
         <v>0</v>
@@ -18683,10 +18683,10 @@
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B301" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C301">
         <v>7000</v>
@@ -18707,7 +18707,7 @@
         <v>359.33782400000001</v>
       </c>
       <c r="I301" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J301">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>248.85695000000001</v>
       </c>
       <c r="Q301" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R301">
         <v>0</v>
@@ -18739,10 +18739,10 @@
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B302" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C302">
         <v>7000</v>
@@ -18763,7 +18763,7 @@
         <v>444.688086</v>
       </c>
       <c r="I302" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J302">
         <v>0</v>
@@ -18775,7 +18775,7 @@
         <v>446.30169999999998</v>
       </c>
       <c r="M302" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N302">
         <v>0</v>
@@ -18787,7 +18787,7 @@
         <v>303.58950199999998</v>
       </c>
       <c r="Q302" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R302">
         <v>0</v>
@@ -18795,10 +18795,10 @@
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B303" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C303">
         <v>7000</v>
@@ -18819,7 +18819,7 @@
         <v>521.31202800000005</v>
       </c>
       <c r="I303" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J303">
         <v>0</v>
@@ -18831,7 +18831,7 @@
         <v>522.54365600000006</v>
       </c>
       <c r="M303" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N303">
         <v>0</v>
@@ -18843,7 +18843,7 @@
         <v>356.58093200000002</v>
       </c>
       <c r="Q303" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R303">
         <v>0</v>
@@ -18851,10 +18851,10 @@
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B304" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C304">
         <v>7000</v>
@@ -18875,7 +18875,7 @@
         <v>128.46249</v>
       </c>
       <c r="I304" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -18887,7 +18887,7 @@
         <v>128.98062999999999</v>
       </c>
       <c r="M304" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N304">
         <v>0</v>
@@ -18899,7 +18899,7 @@
         <v>102.8111</v>
       </c>
       <c r="Q304" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R304">
         <v>0</v>
@@ -18907,10 +18907,10 @@
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B305" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C305">
         <v>7000</v>
@@ -18931,7 +18931,7 @@
         <v>237.008892</v>
       </c>
       <c r="I305" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -18955,7 +18955,7 @@
         <v>191.34121999999999</v>
       </c>
       <c r="Q305" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R305">
         <v>0</v>
@@ -18963,10 +18963,10 @@
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B306" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C306">
         <v>7000</v>
@@ -18987,7 +18987,7 @@
         <v>335.84592800000001</v>
       </c>
       <c r="I306" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -18999,7 +18999,7 @@
         <v>336.75477999999998</v>
       </c>
       <c r="M306" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N306">
         <v>0</v>
@@ -19011,7 +19011,7 @@
         <v>244.14046200000001</v>
       </c>
       <c r="Q306" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R306">
         <v>0</v>
@@ -19019,10 +19019,10 @@
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B307" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C307">
         <v>7000</v>
@@ -19043,7 +19043,7 @@
         <v>426.77555799999999</v>
       </c>
       <c r="I307" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -19067,7 +19067,7 @@
         <v>298.86469199999999</v>
       </c>
       <c r="Q307" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R307">
         <v>0</v>
@@ -19075,10 +19075,10 @@
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B308" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C308">
         <v>7000</v>
@@ -19099,7 +19099,7 @@
         <v>507.820786</v>
       </c>
       <c r="I308" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -19111,7 +19111,7 @@
         <v>510.97776599999997</v>
       </c>
       <c r="M308" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N308">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>352.80276600000002</v>
       </c>
       <c r="Q308" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R308">
         <v>0</v>
@@ -19131,10 +19131,10 @@
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B309" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C309">
         <v>7000</v>
@@ -19179,7 +19179,7 @@
         <v>111.149196</v>
       </c>
       <c r="Q309" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R309">
         <v>0</v>
@@ -19187,10 +19187,10 @@
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B310" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C310">
         <v>7000</v>
@@ -19211,7 +19211,7 @@
         <v>256.37202400000001</v>
       </c>
       <c r="I310" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -19235,7 +19235,7 @@
         <v>188.74712199999999</v>
       </c>
       <c r="Q310" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R310">
         <v>0</v>
@@ -19243,10 +19243,10 @@
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B311" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C311">
         <v>7000</v>
@@ -19267,7 +19267,7 @@
         <v>349.757338</v>
       </c>
       <c r="I311" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>351.253244</v>
       </c>
       <c r="M311" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N311">
         <v>0</v>
@@ -19291,7 +19291,7 @@
         <v>241.229782</v>
       </c>
       <c r="Q311" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R311">
         <v>0</v>
@@ -19299,10 +19299,10 @@
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B312" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C312">
         <v>7000</v>
@@ -19323,7 +19323,7 @@
         <v>436.326908</v>
       </c>
       <c r="I312" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -19335,7 +19335,7 @@
         <v>437.93005199999999</v>
       </c>
       <c r="M312" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N312">
         <v>0</v>
@@ -19347,7 +19347,7 @@
         <v>300.42398800000001</v>
       </c>
       <c r="Q312" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R312">
         <v>0</v>
@@ -19355,10 +19355,10 @@
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B313" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C313">
         <v>7000</v>
@@ -19379,7 +19379,7 @@
         <v>516.53891399999998</v>
       </c>
       <c r="I313" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -19391,7 +19391,7 @@
         <v>519.51113199999998</v>
       </c>
       <c r="M313" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N313">
         <v>0</v>
@@ -19403,7 +19403,7 @@
         <v>367.57217600000001</v>
       </c>
       <c r="Q313" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R313">
         <v>0</v>
@@ -19411,10 +19411,10 @@
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B314" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C314">
         <v>7000</v>
@@ -19435,7 +19435,7 @@
         <v>139.850538</v>
       </c>
       <c r="I314" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -19459,7 +19459,7 @@
         <v>106.000338</v>
       </c>
       <c r="Q314" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R314">
         <v>0</v>
@@ -19467,10 +19467,10 @@
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B315" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C315">
         <v>7000</v>
@@ -19491,7 +19491,7 @@
         <v>247.39899199999999</v>
       </c>
       <c r="I315" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J315">
         <v>0</v>
@@ -19515,7 +19515,7 @@
         <v>176.892144</v>
       </c>
       <c r="Q315" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R315">
         <v>0</v>
@@ -19523,10 +19523,10 @@
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B316" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C316">
         <v>7000</v>
@@ -19547,7 +19547,7 @@
         <v>337.14440000000002</v>
       </c>
       <c r="I316" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J316">
         <v>0</v>
@@ -19571,7 +19571,7 @@
         <v>239.114664</v>
       </c>
       <c r="Q316" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R316">
         <v>0</v>
@@ -19579,10 +19579,10 @@
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B317" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C317">
         <v>7000</v>
@@ -19603,7 +19603,7 @@
         <v>416.27263799999997</v>
       </c>
       <c r="I317" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J317">
         <v>0</v>
@@ -19615,7 +19615,7 @@
         <v>418.72498400000001</v>
       </c>
       <c r="M317" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N317">
         <v>0</v>
@@ -19627,7 +19627,7 @@
         <v>282.34068400000001</v>
       </c>
       <c r="Q317" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R317">
         <v>0</v>
@@ -19635,10 +19635,10 @@
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B318" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C318">
         <v>7000</v>
@@ -19659,7 +19659,7 @@
         <v>491.27867600000002</v>
       </c>
       <c r="I318" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J318">
         <v>0</v>
@@ -19671,7 +19671,7 @@
         <v>493.07862799999998</v>
       </c>
       <c r="M318" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N318">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>360.83122800000001</v>
       </c>
       <c r="Q318" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R318">
         <v>0</v>
@@ -19691,10 +19691,10 @@
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B319" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C319">
         <v>7000</v>
@@ -19739,7 +19739,7 @@
         <v>108.546684</v>
       </c>
       <c r="Q319" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R319">
         <v>0</v>
@@ -19747,10 +19747,10 @@
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B320" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C320">
         <v>7000</v>
@@ -19795,7 +19795,7 @@
         <v>194.13234800000001</v>
       </c>
       <c r="Q320" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R320">
         <v>0</v>
@@ -19803,10 +19803,10 @@
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B321" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C321">
         <v>7000</v>
@@ -19827,7 +19827,7 @@
         <v>388.53235999999998</v>
       </c>
       <c r="I321" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J321">
         <v>0</v>
@@ -19839,7 +19839,7 @@
         <v>389.92920800000002</v>
       </c>
       <c r="M321" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N321">
         <v>0</v>
@@ -19851,7 +19851,7 @@
         <v>261.17338799999999</v>
       </c>
       <c r="Q321" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R321">
         <v>0</v>
@@ -19859,10 +19859,10 @@
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B322" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C322">
         <v>7000</v>
@@ -19883,7 +19883,7 @@
         <v>482.49301200000002</v>
       </c>
       <c r="I322" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J322">
         <v>0</v>
@@ -19895,7 +19895,7 @@
         <v>485.01092199999999</v>
       </c>
       <c r="M322" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N322">
         <v>0</v>
@@ -19907,7 +19907,7 @@
         <v>326.52769999999998</v>
       </c>
       <c r="Q322" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R322">
         <v>0</v>
@@ -19915,10 +19915,10 @@
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B323" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C323">
         <v>7000</v>
@@ -19939,7 +19939,7 @@
         <v>569.81491200000005</v>
       </c>
       <c r="I323" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J323">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>571.191776</v>
       </c>
       <c r="M323" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N323">
         <v>0</v>
@@ -19963,7 +19963,7 @@
         <v>384.203236</v>
       </c>
       <c r="Q323" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R323">
         <v>0</v>
@@ -19971,10 +19971,10 @@
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B324" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C324">
         <v>7000</v>
@@ -20019,7 +20019,7 @@
         <v>115.65856599999999</v>
       </c>
       <c r="Q324" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R324">
         <v>0</v>
@@ -20027,10 +20027,10 @@
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B325" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C325">
         <v>7000</v>
@@ -20051,7 +20051,7 @@
         <v>255.52034399999999</v>
       </c>
       <c r="I325" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J325">
         <v>0</v>
@@ -20075,7 +20075,7 @@
         <v>188.087132</v>
       </c>
       <c r="Q325" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R325">
         <v>0</v>
@@ -20083,10 +20083,10 @@
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B326" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C326">
         <v>7000</v>
@@ -20107,7 +20107,7 @@
         <v>349.11121200000002</v>
       </c>
       <c r="I326" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J326">
         <v>0</v>
@@ -20119,7 +20119,7 @@
         <v>350.09795600000001</v>
       </c>
       <c r="M326" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N326">
         <v>0</v>
@@ -20131,7 +20131,7 @@
         <v>250.31087199999999</v>
       </c>
       <c r="Q326" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R326">
         <v>0</v>
@@ -20139,10 +20139,10 @@
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B327" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C327">
         <v>7000</v>
@@ -20163,7 +20163,7 @@
         <v>432.65671800000001</v>
       </c>
       <c r="I327" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J327">
         <v>0</v>
@@ -20187,7 +20187,7 @@
         <v>303.00376</v>
       </c>
       <c r="Q327" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R327">
         <v>0</v>
@@ -20195,10 +20195,10 @@
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B328" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C328">
         <v>7000</v>
@@ -20219,7 +20219,7 @@
         <v>510.01304199999998</v>
       </c>
       <c r="I328" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J328">
         <v>0</v>
@@ -20231,7 +20231,7 @@
         <v>511.92844000000002</v>
       </c>
       <c r="M328" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N328">
         <v>0</v>
@@ -20243,7 +20243,7 @@
         <v>356.768214</v>
       </c>
       <c r="Q328" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R328">
         <v>0</v>
@@ -20251,10 +20251,10 @@
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B329" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C329">
         <v>7000</v>
@@ -20299,7 +20299,7 @@
         <v>110.116086</v>
       </c>
       <c r="Q329" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R329">
         <v>0</v>
@@ -20307,10 +20307,10 @@
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B330" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C330">
         <v>7000</v>
@@ -20331,7 +20331,7 @@
         <v>255.58998600000001</v>
       </c>
       <c r="I330" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J330">
         <v>0</v>
@@ -20355,7 +20355,7 @@
         <v>198.52690999999999</v>
       </c>
       <c r="Q330" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R330">
         <v>0</v>
@@ -20363,10 +20363,10 @@
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B331" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C331">
         <v>7000</v>
@@ -20387,7 +20387,7 @@
         <v>352.20198399999998</v>
       </c>
       <c r="I331" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -20399,7 +20399,7 @@
         <v>354.64640600000001</v>
       </c>
       <c r="M331" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N331">
         <v>0</v>
@@ -20411,7 +20411,7 @@
         <v>262.12535600000001</v>
       </c>
       <c r="Q331" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R331">
         <v>0</v>
@@ -20419,10 +20419,10 @@
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B332" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C332">
         <v>7000</v>
@@ -20443,7 +20443,7 @@
         <v>442.680902</v>
       </c>
       <c r="I332" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J332">
         <v>0</v>
@@ -20455,7 +20455,7 @@
         <v>446.04652199999998</v>
       </c>
       <c r="M332" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N332">
         <v>0</v>
@@ -20467,7 +20467,7 @@
         <v>317.77804600000002</v>
       </c>
       <c r="Q332" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R332">
         <v>0</v>
@@ -20475,10 +20475,10 @@
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B333" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C333">
         <v>7000</v>
@@ -20499,7 +20499,7 @@
         <v>529.58963400000005</v>
       </c>
       <c r="I333" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J333">
         <v>0</v>
@@ -20511,7 +20511,7 @@
         <v>532.15853200000004</v>
       </c>
       <c r="M333" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N333">
         <v>0</v>
@@ -20523,7 +20523,7 @@
         <v>372.77113000000003</v>
       </c>
       <c r="Q333" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R333">
         <v>0</v>
@@ -20531,7 +20531,7 @@
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B334" s="8"/>
       <c r="C334" s="8">
@@ -20549,7 +20549,7 @@
         <v>4.8658192088435999E-3</v>
       </c>
       <c r="I334" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J334" s="8">
         <f>SUM(J284:J333)</f>
@@ -20564,7 +20564,7 @@
         <v>1.0746154076108939E-3</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N334" s="8">
         <f>SUM(N284:N333)</f>
@@ -20579,7 +20579,7 @@
         <v>0.28800941912995592</v>
       </c>
       <c r="Q334" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R334" s="8">
         <f>SUM(R284:R333)</f>
@@ -20588,10 +20588,10 @@
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B335" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C335">
         <v>9269</v>
@@ -20636,7 +20636,7 @@
         <v>287.65016000000003</v>
       </c>
       <c r="Q335" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R335">
         <v>0</v>
@@ -20644,10 +20644,10 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B336" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C336">
         <v>9269</v>
@@ -20692,7 +20692,7 @@
         <v>449.42952000000002</v>
       </c>
       <c r="Q336" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R336">
         <v>0</v>
@@ -20700,10 +20700,10 @@
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B337" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C337">
         <v>9269</v>
@@ -20724,7 +20724,7 @@
         <v>731.20412599999997</v>
       </c>
       <c r="I337" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -20736,7 +20736,7 @@
         <v>732.48768399999994</v>
       </c>
       <c r="M337" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N337">
         <v>0</v>
@@ -20748,7 +20748,7 @@
         <v>579.71099000000004</v>
       </c>
       <c r="Q337" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R337">
         <v>0</v>
@@ -20756,10 +20756,10 @@
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B338" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C338">
         <v>9269</v>
@@ -20780,7 +20780,7 @@
         <v>851.04265799999996</v>
       </c>
       <c r="I338" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -20792,7 +20792,7 @@
         <v>853.870676</v>
       </c>
       <c r="M338" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N338">
         <v>0</v>
@@ -20804,7 +20804,7 @@
         <v>698.27013399999998</v>
       </c>
       <c r="Q338" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R338">
         <v>0</v>
@@ -20812,10 +20812,10 @@
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B339" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C339">
         <v>9269</v>
@@ -20836,7 +20836,7 @@
         <v>958.19125599999995</v>
       </c>
       <c r="I339" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -20848,7 +20848,7 @@
         <v>961.75901599999997</v>
       </c>
       <c r="M339" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N339">
         <v>0</v>
@@ -20860,7 +20860,7 @@
         <v>782.49938799999995</v>
       </c>
       <c r="Q339" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R339">
         <v>0</v>
@@ -20868,7 +20868,7 @@
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B340" s="8"/>
       <c r="C340" s="8">
@@ -20886,7 +20886,7 @@
         <v>2.6253836724478264E-3</v>
       </c>
       <c r="I340" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J340" s="8">
         <f>SUM(J335:J339)</f>
@@ -20901,7 +20901,7 @@
         <v>7.3982218397589854E-4</v>
       </c>
       <c r="M340" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N340" s="8">
         <f>SUM(N335:N339)</f>
@@ -20916,7 +20916,7 @@
         <v>0.22715683974761475</v>
       </c>
       <c r="Q340" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R340" s="8">
         <f>SUM(R335:R339)</f>
@@ -20925,10 +20925,10 @@
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B341" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C341">
         <v>7159</v>
@@ -20949,7 +20949,7 @@
         <v>138.66751600000001</v>
       </c>
       <c r="I341" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -20961,7 +20961,7 @@
         <v>139.08106000000001</v>
       </c>
       <c r="M341" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N341">
         <v>0</v>
@@ -20973,7 +20973,7 @@
         <v>89.07902</v>
       </c>
       <c r="Q341" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R341">
         <v>0</v>
@@ -20981,10 +20981,10 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B342" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C342">
         <v>7159</v>
@@ -21005,7 +21005,7 @@
         <v>237.604648</v>
       </c>
       <c r="I342" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>239.067678</v>
       </c>
       <c r="M342" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N342">
         <v>0</v>
@@ -21029,7 +21029,7 @@
         <v>154.76698200000001</v>
       </c>
       <c r="Q342" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R342">
         <v>0</v>
@@ -21037,10 +21037,10 @@
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B343" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C343">
         <v>7159</v>
@@ -21061,7 +21061,7 @@
         <v>318.6266</v>
       </c>
       <c r="I343" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -21073,7 +21073,7 @@
         <v>321.97440599999999</v>
       </c>
       <c r="M343" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N343">
         <v>0</v>
@@ -21085,7 +21085,7 @@
         <v>207.87481399999999</v>
       </c>
       <c r="Q343" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R343">
         <v>0</v>
@@ -21093,10 +21093,10 @@
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B344" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C344">
         <v>7159</v>
@@ -21117,7 +21117,7 @@
         <v>390.24020400000001</v>
       </c>
       <c r="I344" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J344">
         <v>0</v>
@@ -21129,7 +21129,7 @@
         <v>393.54638999999997</v>
       </c>
       <c r="M344" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N344">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>268.12577800000003</v>
       </c>
       <c r="Q344" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R344">
         <v>0</v>
@@ -21149,10 +21149,10 @@
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B345" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C345">
         <v>7159</v>
@@ -21173,7 +21173,7 @@
         <v>456.80411400000003</v>
       </c>
       <c r="I345" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -21185,7 +21185,7 @@
         <v>460.202786</v>
       </c>
       <c r="M345" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N345">
         <v>0</v>
@@ -21197,7 +21197,7 @@
         <v>315.58740599999999</v>
       </c>
       <c r="Q345" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R345">
         <v>0</v>
@@ -21205,7 +21205,7 @@
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A346" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B346" s="8"/>
       <c r="C346" s="8">
@@ -21223,7 +21223,7 @@
         <v>1.1733520860246673E-2</v>
       </c>
       <c r="I346" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J346" s="8">
         <f>SUM(J341:J345)</f>
@@ -21238,7 +21238,7 @@
         <v>4.7173804227880747E-3</v>
       </c>
       <c r="M346" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N346" s="8">
         <f ca="1">SUM(N341:N346)</f>
@@ -21253,7 +21253,7 @@
         <v>0.34303550362782015</v>
       </c>
       <c r="Q346" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R346" s="8">
         <f>SUM(R341:R345)</f>
@@ -21262,10 +21262,10 @@
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B347" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C347">
         <v>1021</v>
@@ -21310,7 +21310,7 @@
         <v>72.602789999999999</v>
       </c>
       <c r="Q347" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R347">
         <v>0</v>
@@ -21318,10 +21318,10 @@
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B348" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C348">
         <v>1021</v>
@@ -21366,7 +21366,7 @@
         <v>134.31044600000001</v>
       </c>
       <c r="Q348" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R348">
         <v>0</v>
@@ -21374,10 +21374,10 @@
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B349" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C349">
         <v>1021</v>
@@ -21398,7 +21398,7 @@
         <v>180.52292600000001</v>
       </c>
       <c r="I349" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -21430,10 +21430,10 @@
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B350" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C350">
         <v>1021</v>
@@ -21454,7 +21454,7 @@
         <v>216.418014</v>
       </c>
       <c r="I350" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -21478,7 +21478,7 @@
         <v>215.98654999999999</v>
       </c>
       <c r="Q350" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R350">
         <v>0</v>
@@ -21486,10 +21486,10 @@
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B351" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C351">
         <v>1021</v>
@@ -21534,7 +21534,7 @@
         <v>246.924488</v>
       </c>
       <c r="Q351" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R351">
         <v>0</v>
@@ -21542,7 +21542,7 @@
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A352" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B352" s="8"/>
       <c r="C352" s="8">
@@ -21593,10 +21593,10 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B353" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C353">
         <v>8834</v>
@@ -21649,10 +21649,10 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B354" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C354">
         <v>8834</v>
@@ -21705,10 +21705,10 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B355" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C355">
         <v>8834</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B356" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C356">
         <v>8834</v>
@@ -21817,10 +21817,10 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B357" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C357">
         <v>8834</v>
@@ -21873,7 +21873,7 @@
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A358" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B358" s="8"/>
       <c r="C358" s="8">
@@ -21891,7 +21891,7 @@
         <v>1.1745823146463784E-3</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J358" s="8">
         <f>SUM(J353:J357)</f>
@@ -21906,7 +21906,7 @@
         <v>0</v>
       </c>
       <c r="M358" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N358" s="8">
         <f>SUM(N353:N357)</f>
@@ -21921,7 +21921,7 @@
         <v>2.0986867296829051E-4</v>
       </c>
       <c r="Q358" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R358" s="8">
         <f>SUM(R353:R357)</f>

--- a/summary_results.xlsx
+++ b/summary_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDB844F-AC04-4F60-9067-E7FD9DEB4089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4C2D0-54DE-4549-9E98-4E34EFD908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
   </bookViews>
@@ -2421,7 +2421,7 @@
         <v>11143</v>
       </c>
       <c r="D8">
-        <v>5572</v>
+        <v>5571</v>
       </c>
       <c r="E8" s="1">
         <v>6.1835999999999998E-4</v>

--- a/summary_results.xlsx
+++ b/summary_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\users\thanh tu\Downloads\FCBQP_parallel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4C2D0-54DE-4549-9E98-4E34EFD908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9B5A37-87C1-4026-81B6-9EDBDBB2B6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
   </bookViews>
@@ -9073,7 +9073,7 @@
         <v>3.24225E-2</v>
       </c>
       <c r="F129">
-        <v>19725322.192839898</v>
+        <v>19725322.192839999</v>
       </c>
       <c r="G129">
         <v>19725322.192839999</v>
@@ -9129,7 +9129,7 @@
         <v>3.24225E-2</v>
       </c>
       <c r="F130">
-        <v>23805405.245379899</v>
+        <v>23805405.245379999</v>
       </c>
       <c r="G130">
         <v>23805405.245379899</v>
@@ -9297,7 +9297,7 @@
         <v>3.1032219999999999E-2</v>
       </c>
       <c r="F133">
-        <v>21260902.726679899</v>
+        <v>21260902.726679999</v>
       </c>
       <c r="G133">
         <v>21260902.726679999</v>
@@ -9353,7 +9353,7 @@
         <v>3.1032219999999999E-2</v>
       </c>
       <c r="F134">
-        <v>30495483.292709898</v>
+        <v>30495483.292709999</v>
       </c>
       <c r="G134">
         <v>30495483.292709898</v>
@@ -9409,7 +9409,7 @@
         <v>3.1032219999999999E-2</v>
       </c>
       <c r="F135">
-        <v>38032901.950429901</v>
+        <v>38032901.950429998</v>
       </c>
       <c r="G135">
         <v>38032901.950429797</v>
@@ -9577,7 +9577,7 @@
         <v>2.930408E-2</v>
       </c>
       <c r="F138">
-        <v>22840863.487539899</v>
+        <v>22840863.487539999</v>
       </c>
       <c r="G138">
         <v>22840863.487539999</v>
@@ -9689,7 +9689,7 @@
         <v>2.930408E-2</v>
       </c>
       <c r="F140">
-        <v>55943547.515639901</v>
+        <v>55943547.515639998</v>
       </c>
       <c r="G140">
         <v>55943547.515639998</v>
@@ -9857,7 +9857,7 @@
         <v>3.1367609999999997E-2</v>
       </c>
       <c r="F143">
-        <v>23074932.414009899</v>
+        <v>23074932.414009999</v>
       </c>
       <c r="G143">
         <v>23074932.414009999</v>
@@ -9913,7 +9913,7 @@
         <v>3.1367609999999997E-2</v>
       </c>
       <c r="F144">
-        <v>40469681.9321099</v>
+        <v>40469681.932109997</v>
       </c>
       <c r="G144">
         <v>40469681.932109997</v>
@@ -9969,7 +9969,7 @@
         <v>3.1367609999999997E-2</v>
       </c>
       <c r="F145">
-        <v>62332519.3934699</v>
+        <v>62332519.393469997</v>
       </c>
       <c r="G145">
         <v>62332519.3934699</v>
@@ -12486,7 +12486,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F190">
-        <v>11292398.161482001</v>
+        <v>11292398.161481</v>
       </c>
       <c r="G190">
         <v>11292398.1614813</v>
@@ -12542,7 +12542,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F191">
-        <v>11299940.462685</v>
+        <v>11299940.462684</v>
       </c>
       <c r="G191">
         <v>11299940.4626841</v>
@@ -12598,7 +12598,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F192">
-        <v>11291119.490684001</v>
+        <v>11291119.490683001</v>
       </c>
       <c r="G192">
         <v>11291119.490683099</v>
@@ -12710,7 +12710,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F194">
-        <v>11298430.416818</v>
+        <v>11298430.416817</v>
       </c>
       <c r="G194">
         <v>11298430.416817401</v>
@@ -12766,7 +12766,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F195">
-        <v>11305676.848937901</v>
+        <v>11305676.848937999</v>
       </c>
       <c r="G195">
         <v>11305676.8489378</v>
@@ -12822,7 +12822,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F196">
-        <v>11282910.8806899</v>
+        <v>11282910.880689999</v>
       </c>
       <c r="G196">
         <v>11282909.8929267</v>
@@ -13270,7 +13270,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="F204">
-        <v>11302892.010384001</v>
+        <v>11302892.010383001</v>
       </c>
       <c r="G204">
         <v>11302892.010383099</v>
@@ -13546,11 +13546,11 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8">
         <f t="array" ref="G209">AVERAGE((F189:F208-G189:G208)/F189:F208)</f>
-        <v>8.512985407919487E-6</v>
+        <v>8.512985386658379E-6</v>
       </c>
       <c r="H209" s="8">
         <f t="array" ref="H209">AVERAGE((F189:F208-H189:H208)/F189:F208)</f>
-        <v>6.8271909033567669E-5</v>
+        <v>6.8271909012309473E-5</v>
       </c>
       <c r="I209" s="8" t="s">
         <v>9</v>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="P209" s="10">
         <f t="array" ref="P209">AVERAGE((F189:F208-P189:P208)/F189:F208)</f>
-        <v>3.757193501832543E-6</v>
+        <v>3.7571934805714866E-6</v>
       </c>
       <c r="Q209" s="8" t="s">
         <v>9</v>

--- a/summary_results.xlsx
+++ b/summary_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\users\thanh tu\Downloads\FCBQP_parallel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9B5A37-87C1-4026-81B6-9EDBDBB2B6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D07BD8-885F-4EC3-8E66-4C8652D6FD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
   </bookViews>
@@ -17914,7 +17914,7 @@
         <v>1.53294E-3</v>
       </c>
       <c r="F287">
-        <v>442.88250499999998</v>
+        <v>442.89061500000003</v>
       </c>
       <c r="G287">
         <v>440.69545499999998</v>
@@ -18138,7 +18138,7 @@
         <v>1.5151400000000001E-3</v>
       </c>
       <c r="F291">
-        <v>336.30327499999999</v>
+        <v>336.30565999999999</v>
       </c>
       <c r="G291">
         <v>334.77213499999999</v>
@@ -18194,7 +18194,7 @@
         <v>1.5151400000000001E-3</v>
       </c>
       <c r="F292">
-        <v>416.79459500000002</v>
+        <v>416.79508499999997</v>
       </c>
       <c r="G292">
         <v>415.35574500000001</v>
@@ -18418,7 +18418,7 @@
         <v>1.47196E-3</v>
       </c>
       <c r="F296">
-        <v>388.36351000000002</v>
+        <v>388.39409000000001</v>
       </c>
       <c r="G296">
         <v>388.16667000000001</v>
@@ -18754,7 +18754,7 @@
         <v>1.45773E-3</v>
       </c>
       <c r="F302">
-        <v>446.8252</v>
+        <v>446.82528000000002</v>
       </c>
       <c r="G302">
         <v>446.38364999999999</v>
@@ -19034,7 +19034,7 @@
         <v>1.43808E-3</v>
       </c>
       <c r="F307">
-        <v>428.81319999999999</v>
+        <v>428.83992000000001</v>
       </c>
       <c r="G307">
         <v>427.41764999999998</v>
@@ -19594,7 +19594,7 @@
         <v>1.4316699999999999E-3</v>
       </c>
       <c r="F317">
-        <v>419.41752000000002</v>
+        <v>419.42606999999998</v>
       </c>
       <c r="G317">
         <v>417.48181</v>
@@ -20490,7 +20490,7 @@
         <v>1.4308599999999999E-3</v>
       </c>
       <c r="F333">
-        <v>533.20168999999999</v>
+        <v>533.21672000000001</v>
       </c>
       <c r="G333">
         <v>530.67209000000003</v>
@@ -20542,11 +20542,11 @@
       <c r="F334" s="8"/>
       <c r="G334" s="8">
         <f t="array" ref="G334">AVERAGE((F284:F333-G284:G333)/F284:F333)</f>
-        <v>2.6171694637871562E-3</v>
+        <v>2.6214849643415423E-3</v>
       </c>
       <c r="H334" s="8">
         <f t="array" ref="H334">AVERAGE((F284:F333-H284:H333)/F284:F333)</f>
-        <v>4.8658192088435999E-3</v>
+        <v>4.8701247413402617E-3</v>
       </c>
       <c r="I334" s="8" t="s">
         <v>9</v>
@@ -20557,11 +20557,11 @@
       </c>
       <c r="K334" s="8">
         <f t="array" ref="K334">AVERAGE((F284:F333-K284:K333)/F284:F333)</f>
-        <v>6.3186905902342814E-4</v>
+        <v>6.3619381944724342E-4</v>
       </c>
       <c r="L334" s="8">
         <f t="array" ref="L334">AVERAGE((F284:F333-L284:L333)/F284:F333)</f>
-        <v>1.0746154076108939E-3</v>
+        <v>1.0789381756105482E-3</v>
       </c>
       <c r="M334" s="8" t="s">
         <v>9</v>
@@ -20572,11 +20572,11 @@
       </c>
       <c r="O334" s="10">
         <f t="array" ref="O334">AVERAGE((F284:F333-O284:O333)/F284:F333)</f>
-        <v>0.25265482849687437</v>
+        <v>0.2526580074031784</v>
       </c>
       <c r="P334" s="10">
         <f t="array" ref="P334">AVERAGE((F284:F333-P284:P333)/F284:F333)</f>
-        <v>0.28800941912995592</v>
+        <v>0.28801244013039012</v>
       </c>
       <c r="Q334" s="8" t="s">
         <v>9</v>
@@ -20771,7 +20771,7 @@
         <v>7.1491999999999997E-4</v>
       </c>
       <c r="F338">
-        <v>854.70953999999995</v>
+        <v>854.72222999999997</v>
       </c>
       <c r="G338">
         <v>852.25382999999999</v>
@@ -20879,11 +20879,11 @@
       <c r="F340" s="8"/>
       <c r="G340" s="8">
         <f t="array" ref="G340">AVERAGE((F335:F339-G335:G339)/F335:F339)</f>
-        <v>1.5560968435707671E-3</v>
+        <v>1.5590576978140082E-3</v>
       </c>
       <c r="H340" s="8">
         <f t="array" ref="H340">AVERAGE((F335:F339-H335:H339)/F335:F339)</f>
-        <v>2.6253836724478264E-3</v>
+        <v>2.6283403189026962E-3</v>
       </c>
       <c r="I340" s="8" t="s">
         <v>9</v>
@@ -20894,11 +20894,11 @@
       </c>
       <c r="K340" s="8">
         <f t="array" ref="K340">AVERAGE((F335:F339-K335:K339)/F335:F339)</f>
-        <v>5.592117378351311E-4</v>
+        <v>5.621798468248122E-4</v>
       </c>
       <c r="L340" s="8">
         <f t="array" ref="L340">AVERAGE((F335:F339-L335:L339)/F335:F339)</f>
-        <v>7.3982218397589854E-4</v>
+        <v>7.4278865537821977E-4</v>
       </c>
       <c r="M340" s="8" t="s">
         <v>9</v>
@@ -20909,11 +20909,11 @@
       </c>
       <c r="O340" s="10">
         <f t="array" ref="O340">AVERAGE((F335:F339-O335:O339)/F335:F339)</f>
-        <v>0.1577561189271966</v>
+        <v>0.15775863556590949</v>
       </c>
       <c r="P340" s="10">
         <f t="array" ref="P340">AVERAGE((F335:F339-P335:P339)/F335:F339)</f>
-        <v>0.22715683974761475</v>
+        <v>0.22715926564001485</v>
       </c>
       <c r="Q340" s="8" t="s">
         <v>9</v>
@@ -21108,7 +21108,7 @@
         <v>5.9632000000000001E-4</v>
       </c>
       <c r="F344">
-        <v>397.0994</v>
+        <v>397.10394000000002</v>
       </c>
       <c r="G344">
         <v>392.06358999999998</v>
@@ -21216,11 +21216,11 @@
       <c r="F346" s="8"/>
       <c r="G346" s="8">
         <f t="array" ref="G346">AVERAGE((F341:F345-G341:G345)/F341:F345)</f>
-        <v>8.2246528024432549E-3</v>
+        <v>8.2269103605319936E-3</v>
       </c>
       <c r="H346" s="8">
         <f t="array" ref="H346">AVERAGE((F341:F345-H341:H345)/F341:F345)</f>
-        <v>1.1733520860246673E-2</v>
+        <v>1.1735767919018673E-2</v>
       </c>
       <c r="I346" s="8" t="s">
         <v>9</v>
@@ -21231,11 +21231,11 @@
       </c>
       <c r="K346" s="8">
         <f t="array" ref="K346">AVERAGE((F341:F345-K341:K345)/F341:F345)</f>
-        <v>4.0750592658859615E-3</v>
+        <v>4.0773277962307302E-3</v>
       </c>
       <c r="L346" s="8">
         <f t="array" ref="L346">AVERAGE((F341:F345-L341:L345)/F341:F345)</f>
-        <v>4.7173804227880747E-3</v>
+        <v>4.7196465190507729E-3</v>
       </c>
       <c r="M346" s="8" t="s">
         <v>9</v>
@@ -21246,11 +21246,11 @@
       </c>
       <c r="O346" s="10">
         <f t="array" ref="O346">AVERAGE((F341:F345-O341:O345)/F341:F345)</f>
-        <v>0.31017569725687477</v>
+        <v>0.31017737032213855</v>
       </c>
       <c r="P346" s="10">
         <f t="array" ref="P346">AVERAGE((F341:F345-P341:P345)/F341:F345)</f>
-        <v>0.34303550362782015</v>
+        <v>0.34303704753430464</v>
       </c>
       <c r="Q346" s="8" t="s">
         <v>9</v>

--- a/summary_results.xlsx
+++ b/summary_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Tu\Downloads\FCBQP_parallel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29972222-0232-498A-B496-443C283EBE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2756553-02F2-4571-8F86-F65F752D3D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9540" windowWidth="29040" windowHeight="15720" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82BDEFC4-01A7-4C40-9695-256D581AEFD9}"/>
   </bookViews>
   <sheets>
     <sheet name="FCBQP_1core_5runs_summary" sheetId="1" r:id="rId1"/>
@@ -1214,13 +1214,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
-    <numFmt numFmtId="168" formatCode="0.0000000"/>
-    <numFmt numFmtId="169" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1729,7 +1727,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1742,8 +1740,7 @@
     <xf numFmtId="10" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1753,6 +1750,10 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2113,6 +2114,7 @@
   <cols>
     <col min="1" max="1" width="29.44140625" customWidth="1"/>
     <col min="2" max="2" width="27.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
     <col min="6" max="6" width="24.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
@@ -2127,24 +2129,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="16" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -10939,7 +10941,7 @@
         <f t="array" ref="G160">AVERAGE((F150:F159-G150:G159)/F150:F159)</f>
         <v>4.8344748254018773E-5</v>
       </c>
-      <c r="H160" s="8">
+      <c r="H160" s="12">
         <f t="array" ref="H160">AVERAGE((F150:F159-H150:H159)/F150:F159)</f>
         <v>2.3037513103146826E-4</v>
       </c>
@@ -10961,7 +10963,7 @@
         <f>SUM(N150:N159)</f>
         <v>45</v>
       </c>
-      <c r="O160" s="13">
+      <c r="O160" s="12">
         <f t="array" ref="O160">AVERAGE((F150:F159-O150:O159)/F150:F159)</f>
         <v>1.4982421786531849E-5</v>
       </c>
@@ -12106,11 +12108,11 @@
       <c r="D181" s="8"/>
       <c r="E181" s="9"/>
       <c r="F181" s="8"/>
-      <c r="G181" s="8">
+      <c r="G181" s="12">
         <f t="array" ref="G181">AVERAGE((F161:F180-G161:G180)/F161:F180)</f>
         <v>2.8800199951982885E-4</v>
       </c>
-      <c r="H181" s="8">
+      <c r="H181" s="12">
         <f t="array" ref="H181">AVERAGE((F161:F180-H161:H180)/F161:F180)</f>
         <v>3.9132569547953012E-4</v>
       </c>
@@ -12119,11 +12121,11 @@
         <f>SUM(J161:J180)</f>
         <v>3</v>
       </c>
-      <c r="K181" s="8">
+      <c r="K181" s="12">
         <f t="array" ref="K181">AVERAGE((F161:F180-K161:K180)/F161:F180)</f>
         <v>1.8818171579320272E-4</v>
       </c>
-      <c r="L181" s="8">
+      <c r="L181" s="12">
         <f t="array" ref="L181">AVERAGE((F161:F180-L161:L180)/F161:F180)</f>
         <v>2.1204684058721482E-4</v>
       </c>
@@ -12132,11 +12134,11 @@
         <f>SUM(N161:N180)</f>
         <v>37</v>
       </c>
-      <c r="O181" s="10">
+      <c r="O181" s="12">
         <f t="array" ref="O181">AVERAGE((F161:F180-O161:O180)/F161:F180)</f>
         <v>2.0842144795972422E-4</v>
       </c>
-      <c r="P181" s="10">
+      <c r="P181" s="12">
         <f t="array" ref="P181">AVERAGE((F161:F180-P161:P180)/F161:F180)</f>
         <v>2.5666646118477539E-4</v>
       </c>
@@ -12747,7 +12749,7 @@
         <f t="array" ref="O192">AVERAGE((F182:F191-O182:O191)/F182:F191)</f>
         <v>5.3575608518604454E-6</v>
       </c>
-      <c r="P192" s="10">
+      <c r="P192" s="12">
         <f t="array" ref="P192">AVERAGE((F182:F191-P182:P191)/F182:F191)</f>
         <v>1.2033231401112437E-5</v>
       </c>
@@ -13052,7 +13054,7 @@
         <f t="array" ref="G198">AVERAGE((F193:F197-G193:G197)/F193:F197)</f>
         <v>0</v>
       </c>
-      <c r="H198" s="8">
+      <c r="H198" s="12">
         <f t="array" ref="H198">AVERAGE((F193:F197-H193:H197)/F193:F197)</f>
         <v>1.1745823146463784E-3</v>
       </c>
@@ -13078,7 +13080,7 @@
         <f t="array" ref="O198">AVERAGE((F193:F197-O193:O197)/F193:F197)</f>
         <v>0</v>
       </c>
-      <c r="P198" s="8">
+      <c r="P198" s="12">
         <f t="array" ref="P198">AVERAGE((F193:F197-P193:P197)/F193:F197)</f>
         <v>2.0986867296829051E-4</v>
       </c>
@@ -13383,7 +13385,7 @@
         <f t="array" ref="G204">AVERAGE((F199:F203-G199:G203)/F199:F203)</f>
         <v>8.2027307913297974E-5</v>
       </c>
-      <c r="H204" s="8">
+      <c r="H204" s="12">
         <f t="array" ref="H204">AVERAGE((F199:F203-H199:H203)/F199:F203)</f>
         <v>2.7641821301519539E-4</v>
       </c>
@@ -13405,11 +13407,11 @@
         <f>SUM(N199:N203)</f>
         <v>24</v>
       </c>
-      <c r="O204" s="10">
+      <c r="O204" s="12">
         <f t="array" ref="O204">AVERAGE((F199:F203-O199:O203)/F199:F203)</f>
         <v>2.4393602879305516E-3</v>
       </c>
-      <c r="P204" s="10">
+      <c r="P204" s="12">
         <f t="array" ref="P204">AVERAGE((F199:F203-P199:P203)/F199:F203)</f>
         <v>6.3154452435111395E-3</v>
       </c>
@@ -13606,10 +13608,10 @@
       <c r="F208">
         <v>854.72222999999997</v>
       </c>
-      <c r="G208">
+      <c r="G208" s="16">
         <v>852.25382999999999</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="16">
         <v>851.04265799999996</v>
       </c>
       <c r="I208" t="s">
@@ -13621,8 +13623,8 @@
       <c r="K208">
         <v>854.34204</v>
       </c>
-      <c r="L208">
-        <v>853.870676</v>
+      <c r="L208" s="16">
+        <v>853.78969400000005</v>
       </c>
       <c r="M208" t="s">
         <v>367</v>
@@ -13630,10 +13632,10 @@
       <c r="N208">
         <v>0</v>
       </c>
-      <c r="O208" s="2">
+      <c r="O208" s="18">
         <v>724.39059999999995</v>
       </c>
-      <c r="P208" s="2">
+      <c r="P208" s="18">
         <v>698.27013399999998</v>
       </c>
       <c r="Q208" t="s">
@@ -13710,11 +13712,11 @@
       <c r="D210" s="8"/>
       <c r="E210" s="9"/>
       <c r="F210" s="8"/>
-      <c r="G210" s="8">
+      <c r="G210" s="12">
         <f t="array" ref="G210">AVERAGE((F205:F209-G205:G209)/F205:F209)</f>
         <v>1.5590576978140082E-3</v>
       </c>
-      <c r="H210" s="8">
+      <c r="H210" s="12">
         <f t="array" ref="H210">AVERAGE((F205:F209-H205:H209)/F205:F209)</f>
         <v>2.6283403189026962E-3</v>
       </c>
@@ -13723,24 +13725,24 @@
         <f>SUM(J205:J209)</f>
         <v>6</v>
       </c>
-      <c r="K210" s="8">
+      <c r="K210" s="12">
         <f t="array" ref="K210">AVERAGE((F205:F209-K205:K209)/F205:F209)</f>
         <v>5.621798468248122E-4</v>
       </c>
-      <c r="L210" s="8">
+      <c r="L210" s="12">
         <f t="array" ref="L210">AVERAGE((F205:F209-L205:L209)/F205:F209)</f>
-        <v>7.4278865537821977E-4</v>
+        <v>7.6173796947291673E-4</v>
       </c>
       <c r="M210" s="8"/>
       <c r="N210" s="8">
         <f>SUM(N205:N209)</f>
         <v>9</v>
       </c>
-      <c r="O210" s="10">
+      <c r="O210" s="12">
         <f t="array" ref="O210">AVERAGE((F205:F209-O205:O209)/F205:F209)</f>
         <v>0.15775863556590949</v>
       </c>
-      <c r="P210" s="10">
+      <c r="P210" s="12">
         <f t="array" ref="P210">AVERAGE((F205:F209-P205:P209)/F205:F209)</f>
         <v>0.22715926564001485</v>
       </c>
@@ -13755,7 +13757,7 @@
         <v>392</v>
       </c>
       <c r="B211" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C211">
         <v>7000</v>
@@ -13764,40 +13766,40 @@
         <v>100</v>
       </c>
       <c r="E211" s="1">
-        <v>1.53294E-3</v>
-      </c>
-      <c r="F211">
-        <v>142.71664999999999</v>
-      </c>
-      <c r="G211">
-        <v>142.50523000000001</v>
+        <v>1.5150999999999999E-3</v>
+      </c>
+      <c r="F211" s="7">
+        <v>142.13679999999999</v>
+      </c>
+      <c r="G211" s="7">
+        <v>142.13679999999999</v>
       </c>
       <c r="H211">
-        <v>142.06044</v>
-      </c>
-      <c r="I211" t="s">
-        <v>367</v>
+        <v>142.07524599999999</v>
+      </c>
+      <c r="I211">
+        <v>35.900492999999997</v>
       </c>
       <c r="J211">
-        <v>0</v>
-      </c>
-      <c r="K211">
-        <v>142.71664999999999</v>
-      </c>
-      <c r="L211">
-        <v>142.71664999999999</v>
+        <v>2</v>
+      </c>
+      <c r="K211" s="7">
+        <v>142.13679999999999</v>
+      </c>
+      <c r="L211" s="2">
+        <v>142.13679999999999</v>
       </c>
       <c r="M211">
-        <v>8.920871</v>
+        <v>1.886042</v>
       </c>
       <c r="N211">
         <v>5</v>
       </c>
       <c r="O211" s="2">
-        <v>113.59756</v>
+        <v>97.164249999999996</v>
       </c>
       <c r="P211" s="2">
-        <v>109.171176</v>
+        <v>92.234967999999995</v>
       </c>
       <c r="Q211" t="s">
         <v>367</v>
@@ -13811,7 +13813,7 @@
         <v>392</v>
       </c>
       <c r="B212" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C212">
         <v>7000</v>
@@ -13820,16 +13822,16 @@
         <v>200</v>
       </c>
       <c r="E212" s="1">
-        <v>1.53294E-3</v>
-      </c>
-      <c r="F212">
-        <v>255.61268999999999</v>
-      </c>
-      <c r="G212">
-        <v>254.78677999999999</v>
+        <v>1.5150999999999999E-3</v>
+      </c>
+      <c r="F212" s="7">
+        <v>247.79705999999999</v>
+      </c>
+      <c r="G212" s="7">
+        <v>247.33684</v>
       </c>
       <c r="H212">
-        <v>253.86832000000001</v>
+        <v>246.86539999999999</v>
       </c>
       <c r="I212" t="s">
         <v>367</v>
@@ -13837,23 +13839,23 @@
       <c r="J212">
         <v>0</v>
       </c>
-      <c r="K212">
-        <v>255.5487</v>
-      </c>
-      <c r="L212">
-        <v>255.52598599999999</v>
-      </c>
-      <c r="M212" t="s">
-        <v>367</v>
+      <c r="K212" s="7">
+        <v>247.79705999999999</v>
+      </c>
+      <c r="L212" s="2">
+        <v>247.79705999999999</v>
+      </c>
+      <c r="M212">
+        <v>10.145659</v>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O212" s="2">
-        <v>200.62246999999999</v>
+        <v>173.25054</v>
       </c>
       <c r="P212" s="2">
-        <v>195.100988</v>
+        <v>165.256564</v>
       </c>
       <c r="Q212" t="s">
         <v>367</v>
@@ -13867,7 +13869,7 @@
         <v>392</v>
       </c>
       <c r="B213" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C213">
         <v>7000</v>
@@ -13876,16 +13878,16 @@
         <v>300</v>
       </c>
       <c r="E213" s="1">
-        <v>1.53294E-3</v>
-      </c>
-      <c r="F213">
-        <v>354.48030999999997</v>
-      </c>
-      <c r="G213">
-        <v>353.82341000000002</v>
+        <v>1.5150999999999999E-3</v>
+      </c>
+      <c r="F213" s="7">
+        <v>336.30565999999999</v>
+      </c>
+      <c r="G213" s="7">
+        <v>335.19159000000002</v>
       </c>
       <c r="H213">
-        <v>352.72425500000003</v>
+        <v>334.34724799999998</v>
       </c>
       <c r="I213" t="s">
         <v>367</v>
@@ -13893,11 +13895,11 @@
       <c r="J213">
         <v>0</v>
       </c>
-      <c r="K213">
-        <v>354.41550000000001</v>
-      </c>
-      <c r="L213">
-        <v>354.26472000000001</v>
+      <c r="K213" s="7">
+        <v>336.12635999999998</v>
+      </c>
+      <c r="L213" s="2">
+        <v>336.00854600000002</v>
       </c>
       <c r="M213" t="s">
         <v>367</v>
@@ -13906,10 +13908,10 @@
         <v>0</v>
       </c>
       <c r="O213" s="2">
-        <v>257.99099000000001</v>
+        <v>233.14454000000001</v>
       </c>
       <c r="P213" s="2">
-        <v>247.200424</v>
+        <v>220.39002600000001</v>
       </c>
       <c r="Q213" t="s">
         <v>367</v>
@@ -13923,7 +13925,7 @@
         <v>392</v>
       </c>
       <c r="B214" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C214">
         <v>7000</v>
@@ -13932,16 +13934,16 @@
         <v>400</v>
       </c>
       <c r="E214" s="1">
-        <v>1.53294E-3</v>
-      </c>
-      <c r="F214">
-        <v>442.89061500000003</v>
-      </c>
-      <c r="G214">
-        <v>440.69545499999998</v>
+        <v>1.5150999999999999E-3</v>
+      </c>
+      <c r="F214" s="7">
+        <v>416.78546999999998</v>
+      </c>
+      <c r="G214" s="7">
+        <v>416.33783</v>
       </c>
       <c r="H214">
-        <v>439.66992399999998</v>
+        <v>414.72527400000001</v>
       </c>
       <c r="I214" t="s">
         <v>367</v>
@@ -13949,11 +13951,11 @@
       <c r="J214">
         <v>0</v>
       </c>
-      <c r="K214">
-        <v>442.62848500000001</v>
-      </c>
-      <c r="L214">
-        <v>442.02394700000002</v>
+      <c r="K214" s="7">
+        <v>416.26258999999999</v>
+      </c>
+      <c r="L214" s="2">
+        <v>416.14019200000001</v>
       </c>
       <c r="M214" t="s">
         <v>367</v>
@@ -13962,10 +13964,10 @@
         <v>0</v>
       </c>
       <c r="O214" s="2">
-        <v>303.73565000000002</v>
+        <v>292.04273999999998</v>
       </c>
       <c r="P214" s="2">
-        <v>294.27895599999999</v>
+        <v>280.86408399999999</v>
       </c>
       <c r="Q214" t="s">
         <v>367</v>
@@ -13979,7 +13981,7 @@
         <v>392</v>
       </c>
       <c r="B215" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C215">
         <v>7000</v>
@@ -13988,16 +13990,16 @@
         <v>500</v>
       </c>
       <c r="E215" s="1">
-        <v>1.53294E-3</v>
-      </c>
-      <c r="F215">
-        <v>524.15727000000004</v>
-      </c>
-      <c r="G215">
-        <v>522.10491000000002</v>
+        <v>1.5150999999999999E-3</v>
+      </c>
+      <c r="F215" s="7">
+        <v>488.80971</v>
+      </c>
+      <c r="G215" s="7">
+        <v>486.36331999999999</v>
       </c>
       <c r="H215">
-        <v>521.21795799999995</v>
+        <v>485.09733799999998</v>
       </c>
       <c r="I215" t="s">
         <v>367</v>
@@ -14005,11 +14007,11 @@
       <c r="J215">
         <v>0</v>
       </c>
-      <c r="K215">
-        <v>523.66161</v>
-      </c>
-      <c r="L215">
-        <v>523.14984000000004</v>
+      <c r="K215" s="7">
+        <v>487.98117000000002</v>
+      </c>
+      <c r="L215" s="2">
+        <v>487.77013599999998</v>
       </c>
       <c r="M215" t="s">
         <v>367</v>
@@ -14018,10 +14020,10 @@
         <v>0</v>
       </c>
       <c r="O215" s="2">
-        <v>375.50416999999999</v>
+        <v>349.66496000000001</v>
       </c>
       <c r="P215" s="2">
-        <v>364.401656</v>
+        <v>329.18131199999999</v>
       </c>
       <c r="Q215" t="s">
         <v>367</v>
@@ -14035,7 +14037,7 @@
         <v>392</v>
       </c>
       <c r="B216" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C216">
         <v>7000</v>
@@ -14044,16 +14046,16 @@
         <v>100</v>
       </c>
       <c r="E216" s="1">
-        <v>1.5151400000000001E-3</v>
-      </c>
-      <c r="F216">
-        <v>142.13679999999999</v>
-      </c>
-      <c r="G216">
-        <v>142.03421</v>
+        <v>1.4718800000000001E-3</v>
+      </c>
+      <c r="F216" s="7">
+        <v>160.60842</v>
+      </c>
+      <c r="G216" s="7">
+        <v>160.60103000000001</v>
       </c>
       <c r="H216">
-        <v>141.87070800000001</v>
+        <v>160.489194</v>
       </c>
       <c r="I216" t="s">
         <v>367</v>
@@ -14061,23 +14063,23 @@
       <c r="J216">
         <v>0</v>
       </c>
-      <c r="K216">
-        <v>142.13679999999999</v>
-      </c>
-      <c r="L216">
-        <v>142.13679999999999</v>
+      <c r="K216" s="7">
+        <v>160.60842</v>
+      </c>
+      <c r="L216" s="2">
+        <v>160.60842</v>
       </c>
       <c r="M216">
-        <v>3.824681</v>
+        <v>7.2784230000000001</v>
       </c>
       <c r="N216">
         <v>5</v>
       </c>
       <c r="O216" s="2">
-        <v>97.164249999999996</v>
+        <v>132.23325</v>
       </c>
       <c r="P216" s="2">
-        <v>92.234967999999995</v>
+        <v>125.900102</v>
       </c>
       <c r="Q216" t="s">
         <v>367</v>
@@ -14091,7 +14093,7 @@
         <v>392</v>
       </c>
       <c r="B217" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C217">
         <v>7000</v>
@@ -14100,16 +14102,16 @@
         <v>200</v>
       </c>
       <c r="E217" s="1">
-        <v>1.5151400000000001E-3</v>
-      </c>
-      <c r="F217">
-        <v>247.79705999999999</v>
-      </c>
-      <c r="G217">
-        <v>247.14576</v>
+        <v>1.4718800000000001E-3</v>
+      </c>
+      <c r="F217" s="7">
+        <v>282.06218999999999</v>
+      </c>
+      <c r="G217" s="7">
+        <v>281.37416999999999</v>
       </c>
       <c r="H217">
-        <v>246.53982199999999</v>
+        <v>280.71854000000002</v>
       </c>
       <c r="I217" t="s">
         <v>367</v>
@@ -14117,23 +14119,23 @@
       <c r="J217">
         <v>0</v>
       </c>
-      <c r="K217">
-        <v>247.79705999999999</v>
-      </c>
-      <c r="L217">
-        <v>247.59584799999999</v>
-      </c>
-      <c r="M217">
-        <v>25.431833999999998</v>
+      <c r="K217" s="7">
+        <v>281.72043000000002</v>
+      </c>
+      <c r="L217" s="2">
+        <v>281.68038000000001</v>
+      </c>
+      <c r="M217" t="s">
+        <v>367</v>
       </c>
       <c r="N217">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O217" s="2">
-        <v>173.25054</v>
+        <v>227.864</v>
       </c>
       <c r="P217" s="2">
-        <v>165.256564</v>
+        <v>215.60388599999999</v>
       </c>
       <c r="Q217" t="s">
         <v>367</v>
@@ -14147,7 +14149,7 @@
         <v>392</v>
       </c>
       <c r="B218" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C218">
         <v>7000</v>
@@ -14156,16 +14158,16 @@
         <v>300</v>
       </c>
       <c r="E218" s="1">
-        <v>1.5151400000000001E-3</v>
-      </c>
-      <c r="F218">
-        <v>336.30565999999999</v>
-      </c>
-      <c r="G218">
-        <v>334.77213499999999</v>
+        <v>1.4718800000000001E-3</v>
+      </c>
+      <c r="F218" s="7">
+        <v>388.39409000000001</v>
+      </c>
+      <c r="G218" s="7">
+        <v>387.83159999999998</v>
       </c>
       <c r="H218">
-        <v>334.37756400000001</v>
+        <v>386.90218599999997</v>
       </c>
       <c r="I218" t="s">
         <v>367</v>
@@ -14173,11 +14175,11 @@
       <c r="J218">
         <v>0</v>
       </c>
-      <c r="K218">
-        <v>336.20999499999999</v>
-      </c>
-      <c r="L218">
-        <v>335.78627699999998</v>
+      <c r="K218" s="7">
+        <v>388.11849000000001</v>
+      </c>
+      <c r="L218" s="2">
+        <v>388.03724599999998</v>
       </c>
       <c r="M218" t="s">
         <v>367</v>
@@ -14186,10 +14188,10 @@
         <v>0</v>
       </c>
       <c r="O218" s="2">
-        <v>233.14454000000001</v>
+        <v>294.14433000000002</v>
       </c>
       <c r="P218" s="2">
-        <v>220.39002600000001</v>
+        <v>278.52568600000001</v>
       </c>
       <c r="Q218" t="s">
         <v>367</v>
@@ -14203,7 +14205,7 @@
         <v>392</v>
       </c>
       <c r="B219" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C219">
         <v>7000</v>
@@ -14212,16 +14214,16 @@
         <v>400</v>
       </c>
       <c r="E219" s="1">
-        <v>1.5151400000000001E-3</v>
-      </c>
-      <c r="F219">
-        <v>416.79508499999997</v>
-      </c>
-      <c r="G219">
-        <v>415.35574500000001</v>
+        <v>1.4718800000000001E-3</v>
+      </c>
+      <c r="F219" s="7">
+        <v>483.96174999999999</v>
+      </c>
+      <c r="G219" s="7">
+        <v>483.21778</v>
       </c>
       <c r="H219">
-        <v>414.19503700000001</v>
+        <v>482.178606</v>
       </c>
       <c r="I219" t="s">
         <v>367</v>
@@ -14229,11 +14231,11 @@
       <c r="J219">
         <v>0</v>
       </c>
-      <c r="K219">
-        <v>416.27220499999999</v>
-      </c>
-      <c r="L219">
-        <v>415.79192899999998</v>
+      <c r="K219" s="7">
+        <v>483.50227000000001</v>
+      </c>
+      <c r="L219" s="2">
+        <v>483.25977399999999</v>
       </c>
       <c r="M219" t="s">
         <v>367</v>
@@ -14242,10 +14244,10 @@
         <v>0</v>
       </c>
       <c r="O219" s="2">
-        <v>292.04273999999998</v>
+        <v>378.0489</v>
       </c>
       <c r="P219" s="2">
-        <v>280.86408399999999</v>
+        <v>350.63984399999998</v>
       </c>
       <c r="Q219" t="s">
         <v>367</v>
@@ -14259,7 +14261,7 @@
         <v>392</v>
       </c>
       <c r="B220" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C220">
         <v>7000</v>
@@ -14268,16 +14270,16 @@
         <v>500</v>
       </c>
       <c r="E220" s="1">
-        <v>1.5151400000000001E-3</v>
-      </c>
-      <c r="F220">
-        <v>488.81932499999999</v>
-      </c>
-      <c r="G220">
-        <v>486.396795</v>
+        <v>1.4718800000000001E-3</v>
+      </c>
+      <c r="F220" s="7">
+        <v>572.51418999999999</v>
+      </c>
+      <c r="G220" s="7">
+        <v>571.32264999999995</v>
       </c>
       <c r="H220">
-        <v>485.52062699999999</v>
+        <v>570.08389199999999</v>
       </c>
       <c r="I220" t="s">
         <v>367</v>
@@ -14285,11 +14287,11 @@
       <c r="J220">
         <v>0</v>
       </c>
-      <c r="K220">
-        <v>487.824635</v>
-      </c>
-      <c r="L220">
-        <v>487.507881</v>
+      <c r="K220" s="7">
+        <v>572.46213</v>
+      </c>
+      <c r="L220" s="2">
+        <v>572.22895400000004</v>
       </c>
       <c r="M220" t="s">
         <v>367</v>
@@ -14298,10 +14300,10 @@
         <v>0</v>
       </c>
       <c r="O220" s="2">
-        <v>349.66496000000001</v>
+        <v>424.66541999999998</v>
       </c>
       <c r="P220" s="2">
-        <v>329.18131199999999</v>
+        <v>410.54433999999998</v>
       </c>
       <c r="Q220" t="s">
         <v>367</v>
@@ -14315,7 +14317,7 @@
         <v>392</v>
       </c>
       <c r="B221" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C221">
         <v>7000</v>
@@ -14324,40 +14326,40 @@
         <v>100</v>
       </c>
       <c r="E221" s="1">
-        <v>1.47196E-3</v>
-      </c>
-      <c r="F221">
-        <v>160.60842</v>
-      </c>
-      <c r="G221">
-        <v>160.60103000000001</v>
+        <v>1.4577100000000001E-3</v>
+      </c>
+      <c r="F221" s="7">
+        <v>156.42930999999999</v>
+      </c>
+      <c r="G221" s="7">
+        <v>156.42930999999999</v>
       </c>
       <c r="H221">
-        <v>160.215506</v>
-      </c>
-      <c r="I221" t="s">
-        <v>367</v>
+        <v>156.42930999999999</v>
+      </c>
+      <c r="I221">
+        <v>31.992387000000001</v>
       </c>
       <c r="J221">
-        <v>0</v>
-      </c>
-      <c r="K221">
-        <v>160.60842</v>
-      </c>
-      <c r="L221">
-        <v>160.606942</v>
+        <v>5</v>
+      </c>
+      <c r="K221" s="7">
+        <v>156.42930999999999</v>
+      </c>
+      <c r="L221" s="2">
+        <v>156.42930999999999</v>
       </c>
       <c r="M221">
-        <v>22.229817000000001</v>
+        <v>0.124422</v>
       </c>
       <c r="N221">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O221" s="2">
-        <v>132.23325</v>
+        <v>114.87414</v>
       </c>
       <c r="P221" s="2">
-        <v>125.900102</v>
+        <v>110.80799399999999</v>
       </c>
       <c r="Q221" t="s">
         <v>367</v>
@@ -14371,7 +14373,7 @@
         <v>392</v>
       </c>
       <c r="B222" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C222">
         <v>7000</v>
@@ -14380,16 +14382,16 @@
         <v>200</v>
       </c>
       <c r="E222" s="1">
-        <v>1.47196E-3</v>
-      </c>
-      <c r="F222">
-        <v>282.06218999999999</v>
-      </c>
-      <c r="G222">
-        <v>281.16100999999998</v>
+        <v>1.4577100000000001E-3</v>
+      </c>
+      <c r="F222" s="7">
+        <v>266.12285000000003</v>
+      </c>
+      <c r="G222" s="7">
+        <v>264.99907999999999</v>
       </c>
       <c r="H222">
-        <v>280.17756600000001</v>
+        <v>264.76734599999997</v>
       </c>
       <c r="I222" t="s">
         <v>367</v>
@@ -14397,23 +14399,23 @@
       <c r="J222">
         <v>0</v>
       </c>
-      <c r="K222">
-        <v>281.72043000000002</v>
-      </c>
-      <c r="L222">
-        <v>281.60028</v>
-      </c>
-      <c r="M222" t="s">
-        <v>367</v>
+      <c r="K222" s="7">
+        <v>266.12285000000003</v>
+      </c>
+      <c r="L222" s="2">
+        <v>266.12285000000003</v>
+      </c>
+      <c r="M222">
+        <v>15.113811999999999</v>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O222" s="2">
-        <v>227.864</v>
+        <v>196.67894000000001</v>
       </c>
       <c r="P222" s="2">
-        <v>215.60388599999999</v>
+        <v>189.78016199999999</v>
       </c>
       <c r="Q222" t="s">
         <v>367</v>
@@ -14427,7 +14429,7 @@
         <v>392</v>
       </c>
       <c r="B223" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C223">
         <v>7000</v>
@@ -14436,16 +14438,16 @@
         <v>300</v>
       </c>
       <c r="E223" s="1">
-        <v>1.47196E-3</v>
-      </c>
-      <c r="F223">
-        <v>388.39409000000001</v>
-      </c>
-      <c r="G223">
-        <v>388.16667000000001</v>
+        <v>1.4577100000000001E-3</v>
+      </c>
+      <c r="F223" s="7">
+        <v>361.99662999999998</v>
+      </c>
+      <c r="G223" s="7">
+        <v>360.57880999999998</v>
       </c>
       <c r="H223">
-        <v>387.01029399999999</v>
+        <v>359.54206199999999</v>
       </c>
       <c r="I223" t="s">
         <v>367</v>
@@ -14453,23 +14455,23 @@
       <c r="J223">
         <v>0</v>
       </c>
-      <c r="K223">
-        <v>388.08981999999997</v>
-      </c>
-      <c r="L223">
-        <v>387.996374</v>
-      </c>
-      <c r="M223" t="s">
-        <v>367</v>
+      <c r="K223" s="7">
+        <v>361.99662999999998</v>
+      </c>
+      <c r="L223" s="2">
+        <v>361.82717200000002</v>
+      </c>
+      <c r="M223">
+        <v>25.470011</v>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" s="2">
-        <v>294.14433000000002</v>
+        <v>259.30795999999998</v>
       </c>
       <c r="P223" s="2">
-        <v>278.52568600000001</v>
+        <v>248.85695000000001</v>
       </c>
       <c r="Q223" t="s">
         <v>367</v>
@@ -14483,7 +14485,7 @@
         <v>392</v>
       </c>
       <c r="B224" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C224">
         <v>7000</v>
@@ -14492,16 +14494,16 @@
         <v>400</v>
       </c>
       <c r="E224" s="1">
-        <v>1.47196E-3</v>
-      </c>
-      <c r="F224">
-        <v>483.96174999999999</v>
-      </c>
-      <c r="G224">
-        <v>483.28975000000003</v>
+        <v>1.4577100000000001E-3</v>
+      </c>
+      <c r="F224" s="7">
+        <v>446.82528000000002</v>
+      </c>
+      <c r="G224" s="7">
+        <v>446.10257999999999</v>
       </c>
       <c r="H224">
-        <v>482.48890399999999</v>
+        <v>445.01344</v>
       </c>
       <c r="I224" t="s">
         <v>367</v>
@@ -14509,11 +14511,11 @@
       <c r="J224">
         <v>0</v>
       </c>
-      <c r="K224">
-        <v>483.67795999999998</v>
-      </c>
-      <c r="L224">
-        <v>483.42386800000003</v>
+      <c r="K224" s="7">
+        <v>446.54917999999998</v>
+      </c>
+      <c r="L224" s="2">
+        <v>446.35672199999999</v>
       </c>
       <c r="M224" t="s">
         <v>367</v>
@@ -14522,10 +14524,10 @@
         <v>0</v>
       </c>
       <c r="O224" s="2">
-        <v>378.0489</v>
+        <v>313.39211</v>
       </c>
       <c r="P224" s="2">
-        <v>350.63984399999998</v>
+        <v>303.58950199999998</v>
       </c>
       <c r="Q224" t="s">
         <v>367</v>
@@ -14539,7 +14541,7 @@
         <v>392</v>
       </c>
       <c r="B225" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C225">
         <v>7000</v>
@@ -14548,16 +14550,16 @@
         <v>500</v>
       </c>
       <c r="E225" s="1">
-        <v>1.47196E-3</v>
-      </c>
-      <c r="F225">
-        <v>572.51418999999999</v>
-      </c>
-      <c r="G225">
-        <v>571.32974999999999</v>
+        <v>1.4577100000000001E-3</v>
+      </c>
+      <c r="F225" s="7">
+        <v>523.84563000000003</v>
+      </c>
+      <c r="G225" s="7">
+        <v>521.49216999999999</v>
       </c>
       <c r="H225">
-        <v>570.37675999999999</v>
+        <v>520.29437800000005</v>
       </c>
       <c r="I225" t="s">
         <v>367</v>
@@ -14565,11 +14567,11 @@
       <c r="J225">
         <v>0</v>
       </c>
-      <c r="K225">
-        <v>572.04553999999996</v>
-      </c>
-      <c r="L225">
-        <v>571.93580599999996</v>
+      <c r="K225" s="7">
+        <v>523.46379999999999</v>
+      </c>
+      <c r="L225" s="2">
+        <v>522.92005600000005</v>
       </c>
       <c r="M225" t="s">
         <v>367</v>
@@ -14578,10 +14580,10 @@
         <v>0</v>
       </c>
       <c r="O225" s="2">
-        <v>424.66541999999998</v>
+        <v>376.19797</v>
       </c>
       <c r="P225" s="2">
-        <v>410.54433999999998</v>
+        <v>356.58093200000002</v>
       </c>
       <c r="Q225" t="s">
         <v>367</v>
@@ -14595,7 +14597,7 @@
         <v>392</v>
       </c>
       <c r="B226" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C226">
         <v>7000</v>
@@ -14604,40 +14606,40 @@
         <v>100</v>
       </c>
       <c r="E226" s="1">
-        <v>1.45773E-3</v>
-      </c>
-      <c r="F226">
-        <v>156.42930999999999</v>
-      </c>
-      <c r="G226">
-        <v>156.42930999999999</v>
+        <v>1.43804E-3</v>
+      </c>
+      <c r="F226" s="7">
+        <v>129.36341999999999</v>
+      </c>
+      <c r="G226" s="7">
+        <v>128.81952000000001</v>
       </c>
       <c r="H226">
-        <v>156.293104</v>
-      </c>
-      <c r="I226">
-        <v>7.4099130000000004</v>
+        <v>128.58158399999999</v>
+      </c>
+      <c r="I226" t="s">
+        <v>367</v>
       </c>
       <c r="J226">
-        <v>4</v>
-      </c>
-      <c r="K226">
-        <v>156.42930999999999</v>
-      </c>
-      <c r="L226">
-        <v>156.42930999999999</v>
-      </c>
-      <c r="M226">
-        <v>0.50278699999999998</v>
+        <v>0</v>
+      </c>
+      <c r="K226" s="7">
+        <v>128.98062999999999</v>
+      </c>
+      <c r="L226" s="2">
+        <v>128.98062999999999</v>
+      </c>
+      <c r="M226" t="s">
+        <v>367</v>
       </c>
       <c r="N226">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O226" s="2">
-        <v>114.87414</v>
+        <v>107.87851999999999</v>
       </c>
       <c r="P226" s="2">
-        <v>110.80799399999999</v>
+        <v>102.8111</v>
       </c>
       <c r="Q226" t="s">
         <v>367</v>
@@ -14651,7 +14653,7 @@
         <v>392</v>
       </c>
       <c r="B227" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C227">
         <v>7000</v>
@@ -14660,16 +14662,16 @@
         <v>200</v>
       </c>
       <c r="E227" s="1">
-        <v>1.45773E-3</v>
-      </c>
-      <c r="F227">
-        <v>266.12285000000003</v>
-      </c>
-      <c r="G227">
-        <v>265.62203</v>
+        <v>1.43804E-3</v>
+      </c>
+      <c r="F227" s="7">
+        <v>238.34729999999999</v>
+      </c>
+      <c r="G227" s="7">
+        <v>237.55244999999999</v>
       </c>
       <c r="H227">
-        <v>264.78695800000003</v>
+        <v>237.23088000000001</v>
       </c>
       <c r="I227" t="s">
         <v>367</v>
@@ -14677,23 +14679,23 @@
       <c r="J227">
         <v>0</v>
       </c>
-      <c r="K227">
-        <v>266.12285000000003</v>
-      </c>
-      <c r="L227">
-        <v>266.12156199999998</v>
+      <c r="K227" s="7">
+        <v>238.34729999999999</v>
+      </c>
+      <c r="L227" s="2">
+        <v>238.27177599999999</v>
       </c>
       <c r="M227">
-        <v>7.9811909999999999</v>
+        <v>40.619342000000003</v>
       </c>
       <c r="N227">
         <v>4</v>
       </c>
       <c r="O227" s="2">
-        <v>196.67894000000001</v>
+        <v>195.05267000000001</v>
       </c>
       <c r="P227" s="2">
-        <v>189.78016199999999</v>
+        <v>191.34121999999999</v>
       </c>
       <c r="Q227" t="s">
         <v>367</v>
@@ -14707,7 +14709,7 @@
         <v>392</v>
       </c>
       <c r="B228" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C228">
         <v>7000</v>
@@ -14716,16 +14718,16 @@
         <v>300</v>
       </c>
       <c r="E228" s="1">
-        <v>1.45773E-3</v>
-      </c>
-      <c r="F228">
-        <v>361.99662999999998</v>
-      </c>
-      <c r="G228">
-        <v>360.33089000000001</v>
+        <v>1.43804E-3</v>
+      </c>
+      <c r="F228" s="7">
+        <v>337.32862</v>
+      </c>
+      <c r="G228" s="7">
+        <v>336.08528000000001</v>
       </c>
       <c r="H228">
-        <v>359.33782400000001</v>
+        <v>335.62956400000002</v>
       </c>
       <c r="I228" t="s">
         <v>367</v>
@@ -14733,23 +14735,23 @@
       <c r="J228">
         <v>0</v>
       </c>
-      <c r="K228">
-        <v>361.99662999999998</v>
-      </c>
-      <c r="L228">
-        <v>361.74396000000002</v>
-      </c>
-      <c r="M228">
-        <v>8.8765350000000005</v>
+      <c r="K228" s="7">
+        <v>336.96911999999998</v>
+      </c>
+      <c r="L228" s="2">
+        <v>336.813604</v>
+      </c>
+      <c r="M228" t="s">
+        <v>367</v>
       </c>
       <c r="N228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" s="2">
-        <v>259.30795999999998</v>
+        <v>262.94047</v>
       </c>
       <c r="P228" s="2">
-        <v>248.85695000000001</v>
+        <v>244.14046200000001</v>
       </c>
       <c r="Q228" t="s">
         <v>367</v>
@@ -14763,7 +14765,7 @@
         <v>392</v>
       </c>
       <c r="B229" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C229">
         <v>7000</v>
@@ -14772,16 +14774,16 @@
         <v>400</v>
       </c>
       <c r="E229" s="1">
-        <v>1.45773E-3</v>
-      </c>
-      <c r="F229">
-        <v>446.82528000000002</v>
-      </c>
-      <c r="G229">
-        <v>446.38364999999999</v>
+        <v>1.43804E-3</v>
+      </c>
+      <c r="F229" s="7">
+        <v>428.83992000000001</v>
+      </c>
+      <c r="G229" s="7">
+        <v>427.51029999999997</v>
       </c>
       <c r="H229">
-        <v>444.688086</v>
+        <v>426.78179</v>
       </c>
       <c r="I229" t="s">
         <v>367</v>
@@ -14789,11 +14791,11 @@
       <c r="J229">
         <v>0</v>
       </c>
-      <c r="K229">
-        <v>446.65665000000001</v>
-      </c>
-      <c r="L229">
-        <v>446.30169999999998</v>
+      <c r="K229" s="7">
+        <v>428.80497000000003</v>
+      </c>
+      <c r="L229" s="2">
+        <v>428.64142199999998</v>
       </c>
       <c r="M229" t="s">
         <v>367</v>
@@ -14802,10 +14804,10 @@
         <v>0</v>
       </c>
       <c r="O229" s="2">
-        <v>313.39211</v>
+        <v>319.90992</v>
       </c>
       <c r="P229" s="2">
-        <v>303.58950199999998</v>
+        <v>298.86469199999999</v>
       </c>
       <c r="Q229" t="s">
         <v>367</v>
@@ -14819,7 +14821,7 @@
         <v>392</v>
       </c>
       <c r="B230" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C230">
         <v>7000</v>
@@ -14828,16 +14830,16 @@
         <v>500</v>
       </c>
       <c r="E230" s="1">
-        <v>1.45773E-3</v>
-      </c>
-      <c r="F230">
-        <v>523.84563000000003</v>
-      </c>
-      <c r="G230">
-        <v>521.75994000000003</v>
+        <v>1.43804E-3</v>
+      </c>
+      <c r="F230" s="7">
+        <v>511.22753</v>
+      </c>
+      <c r="G230" s="7">
+        <v>509.09719999999999</v>
       </c>
       <c r="H230">
-        <v>521.31202800000005</v>
+        <v>507.79163399999999</v>
       </c>
       <c r="I230" t="s">
         <v>367</v>
@@ -14845,11 +14847,11 @@
       <c r="J230">
         <v>0</v>
       </c>
-      <c r="K230">
-        <v>523.15422999999998</v>
-      </c>
-      <c r="L230">
-        <v>522.54365600000006</v>
+      <c r="K230" s="7">
+        <v>510.97777000000002</v>
+      </c>
+      <c r="L230" s="2">
+        <v>510.77173599999998</v>
       </c>
       <c r="M230" t="s">
         <v>367</v>
@@ -14858,10 +14860,10 @@
         <v>0</v>
       </c>
       <c r="O230" s="2">
-        <v>376.19797</v>
+        <v>361.03273000000002</v>
       </c>
       <c r="P230" s="2">
-        <v>356.58093200000002</v>
+        <v>354.11626000000001</v>
       </c>
       <c r="Q230" t="s">
         <v>367</v>
@@ -14875,7 +14877,7 @@
         <v>392</v>
       </c>
       <c r="B231" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C231">
         <v>7000</v>
@@ -14884,40 +14886,40 @@
         <v>100</v>
       </c>
       <c r="E231" s="1">
-        <v>1.43808E-3</v>
-      </c>
-      <c r="F231">
-        <v>129.36341999999999</v>
-      </c>
-      <c r="G231">
-        <v>128.79311999999999</v>
+        <v>1.5466900000000001E-3</v>
+      </c>
+      <c r="F231" s="7">
+        <v>147.21297999999999</v>
+      </c>
+      <c r="G231" s="7">
+        <v>147.21297999999999</v>
       </c>
       <c r="H231">
-        <v>128.46249</v>
-      </c>
-      <c r="I231" t="s">
-        <v>367</v>
+        <v>147.184752</v>
+      </c>
+      <c r="I231">
+        <v>17.282883000000002</v>
       </c>
       <c r="J231">
-        <v>0</v>
-      </c>
-      <c r="K231">
-        <v>128.98062999999999</v>
-      </c>
-      <c r="L231">
-        <v>128.98062999999999</v>
-      </c>
-      <c r="M231" t="s">
-        <v>367</v>
+        <v>4</v>
+      </c>
+      <c r="K231" s="7">
+        <v>147.21297999999999</v>
+      </c>
+      <c r="L231" s="2">
+        <v>147.21297999999999</v>
+      </c>
+      <c r="M231">
+        <v>1.4494750000000001</v>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O231" s="2">
-        <v>107.87851999999999</v>
+        <v>113.53071</v>
       </c>
       <c r="P231" s="2">
-        <v>102.8111</v>
+        <v>111.149196</v>
       </c>
       <c r="Q231" t="s">
         <v>367</v>
@@ -14931,7 +14933,7 @@
         <v>392</v>
       </c>
       <c r="B232" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C232">
         <v>7000</v>
@@ -14940,16 +14942,16 @@
         <v>200</v>
       </c>
       <c r="E232" s="1">
-        <v>1.43808E-3</v>
-      </c>
-      <c r="F232">
-        <v>238.34729999999999</v>
-      </c>
-      <c r="G232">
-        <v>237.47512</v>
+        <v>1.5466900000000001E-3</v>
+      </c>
+      <c r="F232" s="7">
+        <v>256.88351</v>
+      </c>
+      <c r="G232" s="7">
+        <v>256.81580000000002</v>
       </c>
       <c r="H232">
-        <v>237.008892</v>
+        <v>256.514926</v>
       </c>
       <c r="I232" t="s">
         <v>367</v>
@@ -14957,23 +14959,23 @@
       <c r="J232">
         <v>0</v>
       </c>
-      <c r="K232">
-        <v>238.34729999999999</v>
-      </c>
-      <c r="L232">
-        <v>238.226294</v>
+      <c r="K232" s="7">
+        <v>256.88351</v>
+      </c>
+      <c r="L232" s="2">
+        <v>256.86658999999997</v>
       </c>
       <c r="M232">
-        <v>31.621143</v>
+        <v>41.127676000000001</v>
       </c>
       <c r="N232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O232" s="2">
-        <v>195.05267000000001</v>
+        <v>217.47901999999999</v>
       </c>
       <c r="P232" s="2">
-        <v>191.34121999999999</v>
+        <v>188.74712199999999</v>
       </c>
       <c r="Q232" t="s">
         <v>367</v>
@@ -14987,7 +14989,7 @@
         <v>392</v>
       </c>
       <c r="B233" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C233">
         <v>7000</v>
@@ -14996,16 +14998,16 @@
         <v>300</v>
       </c>
       <c r="E233" s="1">
-        <v>1.43808E-3</v>
-      </c>
-      <c r="F233">
-        <v>337.32862</v>
-      </c>
-      <c r="G233">
-        <v>336.58855</v>
+        <v>1.5466900000000001E-3</v>
+      </c>
+      <c r="F233" s="7">
+        <v>351.50053000000003</v>
+      </c>
+      <c r="G233" s="7">
+        <v>350.27321000000001</v>
       </c>
       <c r="H233">
-        <v>335.84592800000001</v>
+        <v>349.76402400000001</v>
       </c>
       <c r="I233" t="s">
         <v>367</v>
@@ -15013,11 +15015,11 @@
       <c r="J233">
         <v>0</v>
       </c>
-      <c r="K233">
-        <v>336.93103000000002</v>
-      </c>
-      <c r="L233">
-        <v>336.75477999999998</v>
+      <c r="K233" s="7">
+        <v>351.44675000000001</v>
+      </c>
+      <c r="L233" s="2">
+        <v>351.23800199999999</v>
       </c>
       <c r="M233" t="s">
         <v>367</v>
@@ -15026,10 +15028,10 @@
         <v>0</v>
       </c>
       <c r="O233" s="2">
-        <v>262.94047</v>
+        <v>247.66099</v>
       </c>
       <c r="P233" s="2">
-        <v>244.14046200000001</v>
+        <v>241.229782</v>
       </c>
       <c r="Q233" t="s">
         <v>367</v>
@@ -15043,7 +15045,7 @@
         <v>392</v>
       </c>
       <c r="B234" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C234">
         <v>7000</v>
@@ -15052,16 +15054,16 @@
         <v>400</v>
       </c>
       <c r="E234" s="1">
-        <v>1.43808E-3</v>
-      </c>
-      <c r="F234">
-        <v>428.83992000000001</v>
-      </c>
-      <c r="G234">
-        <v>427.41764999999998</v>
+        <v>1.5466900000000001E-3</v>
+      </c>
+      <c r="F234" s="7">
+        <v>438.72872999999998</v>
+      </c>
+      <c r="G234" s="7">
+        <v>437.07792999999998</v>
       </c>
       <c r="H234">
-        <v>426.77555799999999</v>
+        <v>436.35433799999998</v>
       </c>
       <c r="I234" t="s">
         <v>367</v>
@@ -15069,23 +15071,23 @@
       <c r="J234">
         <v>0</v>
       </c>
-      <c r="K234">
-        <v>428.83992000000001</v>
-      </c>
-      <c r="L234">
-        <v>428.66596800000002</v>
-      </c>
-      <c r="M234">
-        <v>44.995258</v>
+      <c r="K234" s="7">
+        <v>438.15688999999998</v>
+      </c>
+      <c r="L234" s="2">
+        <v>437.86635799999999</v>
+      </c>
+      <c r="M234" t="s">
+        <v>367</v>
       </c>
       <c r="N234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O234" s="2">
-        <v>319.90992</v>
+        <v>326.48577</v>
       </c>
       <c r="P234" s="2">
-        <v>298.86469199999999</v>
+        <v>300.42398800000001</v>
       </c>
       <c r="Q234" t="s">
         <v>367</v>
@@ -15099,7 +15101,7 @@
         <v>392</v>
       </c>
       <c r="B235" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C235">
         <v>7000</v>
@@ -15108,16 +15110,16 @@
         <v>500</v>
       </c>
       <c r="E235" s="1">
-        <v>1.43808E-3</v>
-      </c>
-      <c r="F235">
-        <v>511.22753</v>
-      </c>
-      <c r="G235">
-        <v>509.27987000000002</v>
+        <v>1.5466900000000001E-3</v>
+      </c>
+      <c r="F235" s="7">
+        <v>520.36280999999997</v>
+      </c>
+      <c r="G235" s="7">
+        <v>518.34614999999997</v>
       </c>
       <c r="H235">
-        <v>507.820786</v>
+        <v>516.82395399999996</v>
       </c>
       <c r="I235" t="s">
         <v>367</v>
@@ -15125,11 +15127,11 @@
       <c r="J235">
         <v>0</v>
       </c>
-      <c r="K235">
-        <v>511.12373000000002</v>
-      </c>
-      <c r="L235">
-        <v>510.97776599999997</v>
+      <c r="K235" s="7">
+        <v>520.20045000000005</v>
+      </c>
+      <c r="L235" s="2">
+        <v>519.81827999999996</v>
       </c>
       <c r="M235" t="s">
         <v>367</v>
@@ -15138,10 +15140,10 @@
         <v>0</v>
       </c>
       <c r="O235" s="2">
-        <v>361.03273000000002</v>
+        <v>379.45794999999998</v>
       </c>
       <c r="P235" s="2">
-        <v>352.80276600000002</v>
+        <v>367.57217600000001</v>
       </c>
       <c r="Q235" t="s">
         <v>367</v>
@@ -15155,7 +15157,7 @@
         <v>392</v>
       </c>
       <c r="B236" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C236">
         <v>7000</v>
@@ -15164,40 +15166,40 @@
         <v>100</v>
       </c>
       <c r="E236" s="1">
-        <v>1.5468599999999999E-3</v>
-      </c>
-      <c r="F236">
-        <v>147.21297999999999</v>
-      </c>
-      <c r="G236">
-        <v>147.21297999999999</v>
+        <v>1.43151E-3</v>
+      </c>
+      <c r="F236" s="7">
+        <v>140.00452999999999</v>
+      </c>
+      <c r="G236" s="7">
+        <v>140.00452999999999</v>
       </c>
       <c r="H236">
-        <v>147.17847599999999</v>
+        <v>139.97006200000001</v>
       </c>
       <c r="I236">
-        <v>22.722314999999998</v>
+        <v>30.233725</v>
       </c>
       <c r="J236">
-        <v>4</v>
-      </c>
-      <c r="K236">
-        <v>147.21297999999999</v>
-      </c>
-      <c r="L236">
-        <v>147.21297999999999</v>
+        <v>2</v>
+      </c>
+      <c r="K236" s="7">
+        <v>140.00452999999999</v>
+      </c>
+      <c r="L236" s="2">
+        <v>140.00452999999999</v>
       </c>
       <c r="M236">
-        <v>0.83604000000000001</v>
+        <v>4.022411</v>
       </c>
       <c r="N236">
         <v>5</v>
       </c>
       <c r="O236" s="2">
-        <v>113.53071</v>
+        <v>112.75433</v>
       </c>
       <c r="P236" s="2">
-        <v>111.149196</v>
+        <v>106.000338</v>
       </c>
       <c r="Q236" t="s">
         <v>367</v>
@@ -15211,7 +15213,7 @@
         <v>392</v>
       </c>
       <c r="B237" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C237">
         <v>7000</v>
@@ -15220,16 +15222,16 @@
         <v>200</v>
       </c>
       <c r="E237" s="1">
-        <v>1.5468599999999999E-3</v>
-      </c>
-      <c r="F237">
-        <v>256.88351</v>
-      </c>
-      <c r="G237">
-        <v>256.63941999999997</v>
+        <v>1.43151E-3</v>
+      </c>
+      <c r="F237" s="7">
+        <v>247.84585000000001</v>
+      </c>
+      <c r="G237" s="7">
+        <v>247.76258000000001</v>
       </c>
       <c r="H237">
-        <v>256.37202400000001</v>
+        <v>247.484058</v>
       </c>
       <c r="I237" t="s">
         <v>367</v>
@@ -15237,23 +15239,23 @@
       <c r="J237">
         <v>0</v>
       </c>
-      <c r="K237">
-        <v>256.88351</v>
-      </c>
-      <c r="L237">
-        <v>256.87337600000001</v>
+      <c r="K237" s="7">
+        <v>247.84585000000001</v>
+      </c>
+      <c r="L237" s="2">
+        <v>247.826042</v>
       </c>
       <c r="M237">
-        <v>18.803170000000001</v>
+        <v>10.938629000000001</v>
       </c>
       <c r="N237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O237" s="2">
-        <v>217.47901999999999</v>
+        <v>191.00614999999999</v>
       </c>
       <c r="P237" s="2">
-        <v>188.74712199999999</v>
+        <v>176.892144</v>
       </c>
       <c r="Q237" t="s">
         <v>367</v>
@@ -15267,7 +15269,7 @@
         <v>392</v>
       </c>
       <c r="B238" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C238">
         <v>7000</v>
@@ -15276,16 +15278,16 @@
         <v>300</v>
       </c>
       <c r="E238" s="1">
-        <v>1.5468599999999999E-3</v>
-      </c>
-      <c r="F238">
-        <v>351.50053000000003</v>
-      </c>
-      <c r="G238">
-        <v>350.43957</v>
+        <v>1.43151E-3</v>
+      </c>
+      <c r="F238" s="7">
+        <v>338.79363000000001</v>
+      </c>
+      <c r="G238" s="7">
+        <v>337.77825999999999</v>
       </c>
       <c r="H238">
-        <v>349.757338</v>
+        <v>337.10023799999999</v>
       </c>
       <c r="I238" t="s">
         <v>367</v>
@@ -15293,23 +15295,23 @@
       <c r="J238">
         <v>0</v>
       </c>
-      <c r="K238">
-        <v>351.44675000000001</v>
-      </c>
-      <c r="L238">
-        <v>351.253244</v>
-      </c>
-      <c r="M238" t="s">
-        <v>367</v>
+      <c r="K238" s="7">
+        <v>338.79363000000001</v>
+      </c>
+      <c r="L238" s="2">
+        <v>338.402286</v>
+      </c>
+      <c r="M238">
+        <v>14.330735000000001</v>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O238" s="2">
-        <v>247.66099</v>
+        <v>252.26052999999999</v>
       </c>
       <c r="P238" s="2">
-        <v>241.229782</v>
+        <v>239.114664</v>
       </c>
       <c r="Q238" t="s">
         <v>367</v>
@@ -15323,7 +15325,7 @@
         <v>392</v>
       </c>
       <c r="B239" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C239">
         <v>7000</v>
@@ -15332,16 +15334,16 @@
         <v>400</v>
       </c>
       <c r="E239" s="1">
-        <v>1.5468599999999999E-3</v>
-      </c>
-      <c r="F239">
-        <v>438.72872999999998</v>
-      </c>
-      <c r="G239">
-        <v>437.44524999999999</v>
+        <v>1.43151E-3</v>
+      </c>
+      <c r="F239" s="7">
+        <v>419.42606999999998</v>
+      </c>
+      <c r="G239" s="7">
+        <v>417.01681000000002</v>
       </c>
       <c r="H239">
-        <v>436.326908</v>
+        <v>416.28735</v>
       </c>
       <c r="I239" t="s">
         <v>367</v>
@@ -15349,11 +15351,11 @@
       <c r="J239">
         <v>0</v>
       </c>
-      <c r="K239">
-        <v>438.15708000000001</v>
-      </c>
-      <c r="L239">
-        <v>437.93005199999999</v>
+      <c r="K239" s="7">
+        <v>419.19886000000002</v>
+      </c>
+      <c r="L239" s="2">
+        <v>418.796806</v>
       </c>
       <c r="M239" t="s">
         <v>367</v>
@@ -15362,10 +15364,10 @@
         <v>0</v>
       </c>
       <c r="O239" s="2">
-        <v>326.48577</v>
+        <v>293.32414</v>
       </c>
       <c r="P239" s="2">
-        <v>300.42398800000001</v>
+        <v>282.34068400000001</v>
       </c>
       <c r="Q239" t="s">
         <v>367</v>
@@ -15379,7 +15381,7 @@
         <v>392</v>
       </c>
       <c r="B240" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C240">
         <v>7000</v>
@@ -15388,16 +15390,16 @@
         <v>500</v>
       </c>
       <c r="E240" s="1">
-        <v>1.5468599999999999E-3</v>
-      </c>
-      <c r="F240">
-        <v>520.36280999999997</v>
-      </c>
-      <c r="G240">
-        <v>518.34488999999996</v>
+        <v>1.43151E-3</v>
+      </c>
+      <c r="F240" s="7">
+        <v>494.06198999999998</v>
+      </c>
+      <c r="G240" s="7">
+        <v>492.92237999999998</v>
       </c>
       <c r="H240">
-        <v>516.53891399999998</v>
+        <v>491.379254</v>
       </c>
       <c r="I240" t="s">
         <v>367</v>
@@ -15405,11 +15407,11 @@
       <c r="J240">
         <v>0</v>
       </c>
-      <c r="K240">
-        <v>519.96007999999995</v>
-      </c>
-      <c r="L240">
-        <v>519.51113199999998</v>
+      <c r="K240" s="7">
+        <v>493.52073000000001</v>
+      </c>
+      <c r="L240" s="2">
+        <v>493.12885999999997</v>
       </c>
       <c r="M240" t="s">
         <v>367</v>
@@ -15418,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="O240" s="2">
-        <v>379.45794999999998</v>
+        <v>380.15454999999997</v>
       </c>
       <c r="P240" s="2">
-        <v>367.57217600000001</v>
+        <v>360.83122800000001</v>
       </c>
       <c r="Q240" t="s">
         <v>367</v>
@@ -15435,7 +15437,7 @@
         <v>392</v>
       </c>
       <c r="B241" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C241">
         <v>7000</v>
@@ -15444,40 +15446,40 @@
         <v>100</v>
       </c>
       <c r="E241" s="1">
-        <v>1.4316699999999999E-3</v>
-      </c>
-      <c r="F241">
-        <v>140.00452999999999</v>
-      </c>
-      <c r="G241">
-        <v>139.85902999999999</v>
+        <v>1.5036699999999999E-3</v>
+      </c>
+      <c r="F241" s="7">
+        <v>161.7431</v>
+      </c>
+      <c r="G241" s="7">
+        <v>161.7431</v>
       </c>
       <c r="H241">
-        <v>139.850538</v>
-      </c>
-      <c r="I241" t="s">
-        <v>367</v>
+        <v>161.586772</v>
+      </c>
+      <c r="I241">
+        <v>14.845529000000001</v>
       </c>
       <c r="J241">
-        <v>0</v>
-      </c>
-      <c r="K241">
-        <v>140.00452999999999</v>
-      </c>
-      <c r="L241">
-        <v>140.00452999999999</v>
+        <v>4</v>
+      </c>
+      <c r="K241" s="7">
+        <v>161.7431</v>
+      </c>
+      <c r="L241" s="2">
+        <v>161.7431</v>
       </c>
       <c r="M241">
-        <v>7.3458170000000003</v>
+        <v>5.5432000000000002E-2</v>
       </c>
       <c r="N241">
         <v>5</v>
       </c>
       <c r="O241" s="2">
-        <v>112.75433</v>
+        <v>114.07156999999999</v>
       </c>
       <c r="P241" s="2">
-        <v>106.000338</v>
+        <v>108.546684</v>
       </c>
       <c r="Q241" t="s">
         <v>367</v>
@@ -15491,7 +15493,7 @@
         <v>392</v>
       </c>
       <c r="B242" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C242">
         <v>7000</v>
@@ -15500,16 +15502,16 @@
         <v>200</v>
       </c>
       <c r="E242" s="1">
-        <v>1.4316699999999999E-3</v>
-      </c>
-      <c r="F242">
-        <v>247.84585000000001</v>
-      </c>
-      <c r="G242">
-        <v>247.68423999999999</v>
+        <v>1.5036699999999999E-3</v>
+      </c>
+      <c r="F242" s="7">
+        <v>285.37745999999999</v>
+      </c>
+      <c r="G242" s="7">
+        <v>285.08262999999999</v>
       </c>
       <c r="H242">
-        <v>247.39899199999999</v>
+        <v>284.12598400000002</v>
       </c>
       <c r="I242" t="s">
         <v>367</v>
@@ -15517,23 +15519,23 @@
       <c r="J242">
         <v>0</v>
       </c>
-      <c r="K242">
-        <v>247.84585000000001</v>
-      </c>
-      <c r="L242">
-        <v>247.803718</v>
+      <c r="K242" s="7">
+        <v>285.37745999999999</v>
+      </c>
+      <c r="L242" s="2">
+        <v>285.36749200000003</v>
       </c>
       <c r="M242">
-        <v>43.056511</v>
+        <v>17.195401</v>
       </c>
       <c r="N242">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O242" s="2">
-        <v>191.00614999999999</v>
+        <v>202.87291999999999</v>
       </c>
       <c r="P242" s="2">
-        <v>176.892144</v>
+        <v>194.13234800000001</v>
       </c>
       <c r="Q242" t="s">
         <v>367</v>
@@ -15547,7 +15549,7 @@
         <v>392</v>
       </c>
       <c r="B243" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C243">
         <v>7000</v>
@@ -15556,16 +15558,16 @@
         <v>300</v>
       </c>
       <c r="E243" s="1">
-        <v>1.4316699999999999E-3</v>
-      </c>
-      <c r="F243">
-        <v>338.79363000000001</v>
-      </c>
-      <c r="G243">
-        <v>338.38380999999998</v>
+        <v>1.5036699999999999E-3</v>
+      </c>
+      <c r="F243" s="7">
+        <v>390.66397000000001</v>
+      </c>
+      <c r="G243" s="7">
+        <v>389.07109000000003</v>
       </c>
       <c r="H243">
-        <v>337.14440000000002</v>
+        <v>388.72413399999999</v>
       </c>
       <c r="I243" t="s">
         <v>367</v>
@@ -15573,23 +15575,23 @@
       <c r="J243">
         <v>0</v>
       </c>
-      <c r="K243">
-        <v>338.79363000000001</v>
-      </c>
-      <c r="L243">
-        <v>338.64009600000003</v>
-      </c>
-      <c r="M243">
-        <v>24.907036000000002</v>
+      <c r="K243" s="7">
+        <v>390.24353000000002</v>
+      </c>
+      <c r="L243" s="2">
+        <v>390.11005999999998</v>
+      </c>
+      <c r="M243" t="s">
+        <v>367</v>
       </c>
       <c r="N243">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O243" s="2">
-        <v>252.26052999999999</v>
+        <v>272.95778999999999</v>
       </c>
       <c r="P243" s="2">
-        <v>239.114664</v>
+        <v>261.17338799999999</v>
       </c>
       <c r="Q243" t="s">
         <v>367</v>
@@ -15603,7 +15605,7 @@
         <v>392</v>
       </c>
       <c r="B244" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C244">
         <v>7000</v>
@@ -15612,16 +15614,16 @@
         <v>400</v>
       </c>
       <c r="E244" s="1">
-        <v>1.4316699999999999E-3</v>
-      </c>
-      <c r="F244">
-        <v>419.42606999999998</v>
-      </c>
-      <c r="G244">
-        <v>417.48181</v>
+        <v>1.5036699999999999E-3</v>
+      </c>
+      <c r="F244" s="7">
+        <v>485.51931999999999</v>
+      </c>
+      <c r="G244" s="7">
+        <v>483.50990000000002</v>
       </c>
       <c r="H244">
-        <v>416.27263799999997</v>
+        <v>482.97663</v>
       </c>
       <c r="I244" t="s">
         <v>367</v>
@@ -15629,11 +15631,11 @@
       <c r="J244">
         <v>0</v>
       </c>
-      <c r="K244">
-        <v>418.8999</v>
-      </c>
-      <c r="L244">
-        <v>418.72498400000001</v>
+      <c r="K244" s="7">
+        <v>485.08031999999997</v>
+      </c>
+      <c r="L244" s="2">
+        <v>484.88711799999999</v>
       </c>
       <c r="M244" t="s">
         <v>367</v>
@@ -15642,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="O244" s="2">
-        <v>293.32414</v>
+        <v>365.34737000000001</v>
       </c>
       <c r="P244" s="2">
-        <v>282.34068400000001</v>
+        <v>326.52769999999998</v>
       </c>
       <c r="Q244" t="s">
         <v>367</v>
@@ -15659,7 +15661,7 @@
         <v>392</v>
       </c>
       <c r="B245" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C245">
         <v>7000</v>
@@ -15668,16 +15670,16 @@
         <v>500</v>
       </c>
       <c r="E245" s="1">
-        <v>1.4316699999999999E-3</v>
-      </c>
-      <c r="F245">
-        <v>494.06198999999998</v>
-      </c>
-      <c r="G245">
-        <v>492.44011999999998</v>
+        <v>1.5036699999999999E-3</v>
+      </c>
+      <c r="F245" s="7">
+        <v>572.19514000000004</v>
+      </c>
+      <c r="G245" s="7">
+        <v>571.32731999999999</v>
       </c>
       <c r="H245">
-        <v>491.27867600000002</v>
+        <v>569.55937400000005</v>
       </c>
       <c r="I245" t="s">
         <v>367</v>
@@ -15685,11 +15687,11 @@
       <c r="J245">
         <v>0</v>
       </c>
-      <c r="K245">
-        <v>493.46212000000003</v>
-      </c>
-      <c r="L245">
-        <v>493.07862799999998</v>
+      <c r="K245" s="7">
+        <v>571.69277</v>
+      </c>
+      <c r="L245" s="2">
+        <v>571.36655800000005</v>
       </c>
       <c r="M245" t="s">
         <v>367</v>
@@ -15698,10 +15700,10 @@
         <v>0</v>
       </c>
       <c r="O245" s="2">
-        <v>380.15454999999997</v>
+        <v>394.62335000000002</v>
       </c>
       <c r="P245" s="2">
-        <v>360.83122800000001</v>
+        <v>384.203236</v>
       </c>
       <c r="Q245" t="s">
         <v>367</v>
@@ -15715,7 +15717,7 @@
         <v>392</v>
       </c>
       <c r="B246" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C246">
         <v>7000</v>
@@ -15724,40 +15726,40 @@
         <v>100</v>
       </c>
       <c r="E246" s="1">
-        <v>1.50373E-3</v>
-      </c>
-      <c r="F246">
-        <v>161.7431</v>
-      </c>
-      <c r="G246">
-        <v>161.7431</v>
+        <v>1.5784900000000001E-3</v>
+      </c>
+      <c r="F246" s="7">
+        <v>147.46025</v>
+      </c>
+      <c r="G246" s="7">
+        <v>147.46025</v>
       </c>
       <c r="H246">
-        <v>161.05237199999999</v>
+        <v>147.309606</v>
       </c>
       <c r="I246">
-        <v>46.228766</v>
+        <v>13.565963999999999</v>
       </c>
       <c r="J246">
-        <v>1</v>
-      </c>
-      <c r="K246">
-        <v>161.7431</v>
-      </c>
-      <c r="L246">
-        <v>161.7431</v>
+        <v>4</v>
+      </c>
+      <c r="K246" s="7">
+        <v>147.46025</v>
+      </c>
+      <c r="L246" s="2">
+        <v>147.46025</v>
       </c>
       <c r="M246">
-        <v>0.116628</v>
+        <v>0.15137300000000001</v>
       </c>
       <c r="N246">
         <v>5</v>
       </c>
       <c r="O246" s="2">
-        <v>114.07156999999999</v>
+        <v>119.34896000000001</v>
       </c>
       <c r="P246" s="2">
-        <v>108.546684</v>
+        <v>115.65856599999999</v>
       </c>
       <c r="Q246" t="s">
         <v>367</v>
@@ -15771,7 +15773,7 @@
         <v>392</v>
       </c>
       <c r="B247" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C247">
         <v>7000</v>
@@ -15780,40 +15782,40 @@
         <v>200</v>
       </c>
       <c r="E247" s="1">
-        <v>1.50373E-3</v>
-      </c>
-      <c r="F247">
-        <v>285.37745999999999</v>
-      </c>
-      <c r="G247">
-        <v>285.37745999999999</v>
+        <v>1.5784900000000001E-3</v>
+      </c>
+      <c r="F247" s="7">
+        <v>256.29746</v>
+      </c>
+      <c r="G247" s="7">
+        <v>255.92662000000001</v>
       </c>
       <c r="H247">
-        <v>284.56900400000001</v>
-      </c>
-      <c r="I247">
-        <v>6.471571</v>
+        <v>255.61946800000001</v>
+      </c>
+      <c r="I247" t="s">
+        <v>367</v>
       </c>
       <c r="J247">
-        <v>1</v>
-      </c>
-      <c r="K247">
-        <v>285.37745999999999</v>
-      </c>
-      <c r="L247">
-        <v>285.37745999999999</v>
+        <v>0</v>
+      </c>
+      <c r="K247" s="7">
+        <v>256.29746</v>
+      </c>
+      <c r="L247" s="2">
+        <v>256.26906000000002</v>
       </c>
       <c r="M247">
-        <v>6.3148140000000001</v>
+        <v>18.806948999999999</v>
       </c>
       <c r="N247">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O247" s="2">
-        <v>202.87291999999999</v>
+        <v>198.96678</v>
       </c>
       <c r="P247" s="2">
-        <v>194.13234800000001</v>
+        <v>188.087132</v>
       </c>
       <c r="Q247" t="s">
         <v>367</v>
@@ -15827,7 +15829,7 @@
         <v>392</v>
       </c>
       <c r="B248" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C248">
         <v>7000</v>
@@ -15836,16 +15838,16 @@
         <v>300</v>
       </c>
       <c r="E248" s="1">
-        <v>1.50373E-3</v>
-      </c>
-      <c r="F248">
-        <v>390.66397000000001</v>
-      </c>
-      <c r="G248">
-        <v>389.47016000000002</v>
+        <v>1.5784900000000001E-3</v>
+      </c>
+      <c r="F248" s="7">
+        <v>350.39949999999999</v>
+      </c>
+      <c r="G248" s="7">
+        <v>349.88108999999997</v>
       </c>
       <c r="H248">
-        <v>388.53235999999998</v>
+        <v>349.34956399999999</v>
       </c>
       <c r="I248" t="s">
         <v>367</v>
@@ -15853,11 +15855,11 @@
       <c r="J248">
         <v>0</v>
       </c>
-      <c r="K248">
-        <v>390.02454999999998</v>
-      </c>
-      <c r="L248">
-        <v>389.92920800000002</v>
+      <c r="K248" s="7">
+        <v>350.32562000000001</v>
+      </c>
+      <c r="L248" s="2">
+        <v>350.04558400000002</v>
       </c>
       <c r="M248" t="s">
         <v>367</v>
@@ -15866,10 +15868,10 @@
         <v>0</v>
       </c>
       <c r="O248" s="2">
-        <v>272.95778999999999</v>
+        <v>267.4271</v>
       </c>
       <c r="P248" s="2">
-        <v>261.17338799999999</v>
+        <v>250.31087199999999</v>
       </c>
       <c r="Q248" t="s">
         <v>367</v>
@@ -15883,7 +15885,7 @@
         <v>392</v>
       </c>
       <c r="B249" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C249">
         <v>7000</v>
@@ -15892,16 +15894,16 @@
         <v>400</v>
       </c>
       <c r="E249" s="1">
-        <v>1.50373E-3</v>
-      </c>
-      <c r="F249">
-        <v>485.51931999999999</v>
-      </c>
-      <c r="G249">
-        <v>483.26459999999997</v>
+        <v>1.5784900000000001E-3</v>
+      </c>
+      <c r="F249" s="7">
+        <v>435.43218000000002</v>
+      </c>
+      <c r="G249" s="7">
+        <v>433.68650000000002</v>
       </c>
       <c r="H249">
-        <v>482.49301200000002</v>
+        <v>432.94922000000003</v>
       </c>
       <c r="I249" t="s">
         <v>367</v>
@@ -15909,11 +15911,11 @@
       <c r="J249">
         <v>0</v>
       </c>
-      <c r="K249">
-        <v>485.29138</v>
-      </c>
-      <c r="L249">
-        <v>485.01092199999999</v>
+      <c r="K249" s="7">
+        <v>435.32171</v>
+      </c>
+      <c r="L249" s="2">
+        <v>435.05330800000002</v>
       </c>
       <c r="M249" t="s">
         <v>367</v>
@@ -15922,10 +15924,10 @@
         <v>0</v>
       </c>
       <c r="O249" s="2">
-        <v>365.34737000000001</v>
+        <v>314.36304000000001</v>
       </c>
       <c r="P249" s="2">
-        <v>326.52769999999998</v>
+        <v>303.00376</v>
       </c>
       <c r="Q249" t="s">
         <v>367</v>
@@ -15939,7 +15941,7 @@
         <v>392</v>
       </c>
       <c r="B250" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C250">
         <v>7000</v>
@@ -15948,16 +15950,16 @@
         <v>500</v>
       </c>
       <c r="E250" s="1">
-        <v>1.50373E-3</v>
-      </c>
-      <c r="F250">
-        <v>572.19514000000004</v>
-      </c>
-      <c r="G250">
-        <v>571.18679999999995</v>
+        <v>1.5784900000000001E-3</v>
+      </c>
+      <c r="F250" s="7">
+        <v>512.72307999999998</v>
+      </c>
+      <c r="G250" s="7">
+        <v>510.50017000000003</v>
       </c>
       <c r="H250">
-        <v>569.81491200000005</v>
+        <v>509.44511999999997</v>
       </c>
       <c r="I250" t="s">
         <v>367</v>
@@ -15965,11 +15967,11 @@
       <c r="J250">
         <v>0</v>
       </c>
-      <c r="K250">
-        <v>571.38815</v>
-      </c>
-      <c r="L250">
-        <v>571.191776</v>
+      <c r="K250" s="7">
+        <v>512.23825999999997</v>
+      </c>
+      <c r="L250" s="2">
+        <v>511.95080000000002</v>
       </c>
       <c r="M250" t="s">
         <v>367</v>
@@ -15978,10 +15980,10 @@
         <v>0</v>
       </c>
       <c r="O250" s="2">
-        <v>394.62335000000002</v>
+        <v>379.13231999999999</v>
       </c>
       <c r="P250" s="2">
-        <v>384.203236</v>
+        <v>356.768214</v>
       </c>
       <c r="Q250" t="s">
         <v>367</v>
@@ -15995,7 +15997,7 @@
         <v>392</v>
       </c>
       <c r="B251" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C251">
         <v>7000</v>
@@ -16004,40 +16006,40 @@
         <v>100</v>
       </c>
       <c r="E251" s="1">
-        <v>1.5786299999999999E-3</v>
-      </c>
-      <c r="F251">
-        <v>147.46025</v>
-      </c>
-      <c r="G251">
-        <v>147.46025</v>
+        <v>1.43082E-3</v>
+      </c>
+      <c r="F251" s="7">
+        <v>145.03611000000001</v>
+      </c>
+      <c r="G251" s="7">
+        <v>145.03611000000001</v>
       </c>
       <c r="H251">
-        <v>147.46025</v>
+        <v>145.03611000000001</v>
       </c>
       <c r="I251">
-        <v>23.421669999999999</v>
+        <v>14.660428</v>
       </c>
       <c r="J251">
         <v>5</v>
       </c>
-      <c r="K251">
-        <v>147.46025</v>
-      </c>
-      <c r="L251">
-        <v>147.46025</v>
+      <c r="K251" s="7">
+        <v>145.03611000000001</v>
+      </c>
+      <c r="L251" s="2">
+        <v>145.03611000000001</v>
       </c>
       <c r="M251">
-        <v>0.60790999999999995</v>
+        <v>1.7902180000000001</v>
       </c>
       <c r="N251">
         <v>5</v>
       </c>
       <c r="O251" s="2">
-        <v>119.34896000000001</v>
+        <v>115.83778</v>
       </c>
       <c r="P251" s="2">
-        <v>115.65856599999999</v>
+        <v>110.116086</v>
       </c>
       <c r="Q251" t="s">
         <v>367</v>
@@ -16051,7 +16053,7 @@
         <v>392</v>
       </c>
       <c r="B252" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C252">
         <v>7000</v>
@@ -16060,16 +16062,16 @@
         <v>200</v>
       </c>
       <c r="E252" s="1">
-        <v>1.5786299999999999E-3</v>
-      </c>
-      <c r="F252">
-        <v>256.29746</v>
-      </c>
-      <c r="G252">
-        <v>255.91072</v>
+        <v>1.43082E-3</v>
+      </c>
+      <c r="F252" s="7">
+        <v>257.40258999999998</v>
+      </c>
+      <c r="G252" s="7">
+        <v>256.69211000000001</v>
       </c>
       <c r="H252">
-        <v>255.52034399999999</v>
+        <v>255.76541399999999</v>
       </c>
       <c r="I252" t="s">
         <v>367</v>
@@ -16077,23 +16079,23 @@
       <c r="J252">
         <v>0</v>
       </c>
-      <c r="K252">
-        <v>256.29746</v>
-      </c>
-      <c r="L252">
-        <v>256.21625999999998</v>
+      <c r="K252" s="7">
+        <v>257.40258999999998</v>
+      </c>
+      <c r="L252" s="2">
+        <v>257.26673</v>
       </c>
       <c r="M252">
-        <v>41.990220999999998</v>
+        <v>19.674662999999999</v>
       </c>
       <c r="N252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" s="2">
-        <v>198.96678</v>
+        <v>209.70851999999999</v>
       </c>
       <c r="P252" s="2">
-        <v>188.087132</v>
+        <v>198.52690999999999</v>
       </c>
       <c r="Q252" t="s">
         <v>367</v>
@@ -16107,7 +16109,7 @@
         <v>392</v>
       </c>
       <c r="B253" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C253">
         <v>7000</v>
@@ -16116,16 +16118,16 @@
         <v>300</v>
       </c>
       <c r="E253" s="1">
-        <v>1.5786299999999999E-3</v>
-      </c>
-      <c r="F253">
-        <v>350.39949999999999</v>
-      </c>
-      <c r="G253">
-        <v>349.89794999999998</v>
+        <v>1.43082E-3</v>
+      </c>
+      <c r="F253" s="7">
+        <v>356.18635999999998</v>
+      </c>
+      <c r="G253" s="7">
+        <v>353.43759999999997</v>
       </c>
       <c r="H253">
-        <v>349.11121200000002</v>
+        <v>351.74221199999999</v>
       </c>
       <c r="I253" t="s">
         <v>367</v>
@@ -16133,11 +16135,11 @@
       <c r="J253">
         <v>0</v>
       </c>
-      <c r="K253">
-        <v>350.32562000000001</v>
-      </c>
-      <c r="L253">
-        <v>350.09795600000001</v>
+      <c r="K253" s="7">
+        <v>354.93324000000001</v>
+      </c>
+      <c r="L253" s="2">
+        <v>354.54055199999999</v>
       </c>
       <c r="M253" t="s">
         <v>367</v>
@@ -16146,10 +16148,10 @@
         <v>0</v>
       </c>
       <c r="O253" s="2">
-        <v>267.4271</v>
+        <v>265.5181</v>
       </c>
       <c r="P253" s="2">
-        <v>250.31087199999999</v>
+        <v>262.12535600000001</v>
       </c>
       <c r="Q253" t="s">
         <v>367</v>
@@ -16163,7 +16165,7 @@
         <v>392</v>
       </c>
       <c r="B254" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C254">
         <v>7000</v>
@@ -16172,16 +16174,16 @@
         <v>400</v>
       </c>
       <c r="E254" s="1">
-        <v>1.5786299999999999E-3</v>
-      </c>
-      <c r="F254">
-        <v>435.43218000000002</v>
-      </c>
-      <c r="G254">
-        <v>433.73253</v>
+        <v>1.43082E-3</v>
+      </c>
+      <c r="F254" s="7">
+        <v>447.37688000000003</v>
+      </c>
+      <c r="G254" s="7">
+        <v>444.19513000000001</v>
       </c>
       <c r="H254">
-        <v>432.65671800000001</v>
+        <v>443.39804600000002</v>
       </c>
       <c r="I254" t="s">
         <v>367</v>
@@ -16189,23 +16191,23 @@
       <c r="J254">
         <v>0</v>
       </c>
-      <c r="K254">
-        <v>435.43218000000002</v>
-      </c>
-      <c r="L254">
-        <v>435.06743399999999</v>
-      </c>
-      <c r="M254">
-        <v>28.372845999999999</v>
+      <c r="K254" s="7">
+        <v>446.64213999999998</v>
+      </c>
+      <c r="L254" s="2">
+        <v>446.211344</v>
+      </c>
+      <c r="M254" t="s">
+        <v>367</v>
       </c>
       <c r="N254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O254" s="2">
-        <v>314.36304000000001</v>
+        <v>328.1669</v>
       </c>
       <c r="P254" s="2">
-        <v>303.00376</v>
+        <v>317.77804600000002</v>
       </c>
       <c r="Q254" t="s">
         <v>367</v>
@@ -16219,7 +16221,7 @@
         <v>392</v>
       </c>
       <c r="B255" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C255">
         <v>7000</v>
@@ -16228,16 +16230,16 @@
         <v>500</v>
       </c>
       <c r="E255" s="1">
-        <v>1.5786299999999999E-3</v>
-      </c>
-      <c r="F255">
-        <v>512.72307999999998</v>
-      </c>
-      <c r="G255">
-        <v>511.16978</v>
+        <v>1.43082E-3</v>
+      </c>
+      <c r="F255" s="7">
+        <v>533.21672000000001</v>
+      </c>
+      <c r="G255" s="7">
+        <v>530.05841999999996</v>
       </c>
       <c r="H255">
-        <v>510.01304199999998</v>
+        <v>529.08722599999999</v>
       </c>
       <c r="I255" t="s">
         <v>367</v>
@@ -16245,11 +16247,11 @@
       <c r="J255">
         <v>0</v>
       </c>
-      <c r="K255">
-        <v>512.27072999999996</v>
-      </c>
-      <c r="L255">
-        <v>511.92844000000002</v>
+      <c r="K255" s="7">
+        <v>532.58043999999995</v>
+      </c>
+      <c r="L255" s="2">
+        <v>532.263868</v>
       </c>
       <c r="M255" t="s">
         <v>367</v>
@@ -16258,10 +16260,10 @@
         <v>0</v>
       </c>
       <c r="O255" s="2">
-        <v>379.13231999999999</v>
+        <v>381.12632000000002</v>
       </c>
       <c r="P255" s="2">
-        <v>356.768214</v>
+        <v>372.77113000000003</v>
       </c>
       <c r="Q255" t="s">
         <v>367</v>
@@ -16275,7 +16277,7 @@
         <v>392</v>
       </c>
       <c r="B256" t="s">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="C256">
         <v>7000</v>
@@ -16284,40 +16286,40 @@
         <v>100</v>
       </c>
       <c r="E256" s="1">
-        <v>1.4308599999999999E-3</v>
-      </c>
-      <c r="F256">
-        <v>145.03611000000001</v>
-      </c>
-      <c r="G256">
-        <v>145.03611000000001</v>
+        <v>1.5328200000000001E-3</v>
+      </c>
+      <c r="F256" s="7">
+        <v>142.71664999999999</v>
+      </c>
+      <c r="G256" s="7">
+        <v>142.71664999999999</v>
       </c>
       <c r="H256">
-        <v>145.03163599999999</v>
+        <v>142.00546</v>
       </c>
       <c r="I256">
-        <v>35.157010999999997</v>
+        <v>44.247017</v>
       </c>
       <c r="J256">
-        <v>4</v>
-      </c>
-      <c r="K256">
-        <v>145.03611000000001</v>
-      </c>
-      <c r="L256">
-        <v>145.03611000000001</v>
+        <v>1</v>
+      </c>
+      <c r="K256" s="7">
+        <v>142.71664999999999</v>
+      </c>
+      <c r="L256" s="2">
+        <v>142.71664999999999</v>
       </c>
       <c r="M256">
-        <v>2.1334599999999999</v>
+        <v>1.36968</v>
       </c>
       <c r="N256">
         <v>5</v>
       </c>
       <c r="O256" s="2">
-        <v>115.83778</v>
+        <v>113.59756</v>
       </c>
       <c r="P256" s="2">
-        <v>110.116086</v>
+        <v>109.171176</v>
       </c>
       <c r="Q256" t="s">
         <v>367</v>
@@ -16331,7 +16333,7 @@
         <v>392</v>
       </c>
       <c r="B257" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="C257">
         <v>7000</v>
@@ -16340,16 +16342,16 @@
         <v>200</v>
       </c>
       <c r="E257" s="1">
-        <v>1.4308599999999999E-3</v>
-      </c>
-      <c r="F257">
-        <v>257.40258999999998</v>
-      </c>
-      <c r="G257">
-        <v>256.70634000000001</v>
+        <v>1.5328200000000001E-3</v>
+      </c>
+      <c r="F257" s="7">
+        <v>255.61268999999999</v>
+      </c>
+      <c r="G257" s="7">
+        <v>255.14313999999999</v>
       </c>
       <c r="H257">
-        <v>255.58998600000001</v>
+        <v>254.44111000000001</v>
       </c>
       <c r="I257" t="s">
         <v>367</v>
@@ -16357,23 +16359,23 @@
       <c r="J257">
         <v>0</v>
       </c>
-      <c r="K257">
-        <v>257.40258999999998</v>
-      </c>
-      <c r="L257">
-        <v>257.28757400000001</v>
-      </c>
-      <c r="M257">
-        <v>5.9013400000000003</v>
+      <c r="K257" s="7">
+        <v>255.5487</v>
+      </c>
+      <c r="L257" s="2">
+        <v>255.54099199999999</v>
+      </c>
+      <c r="M257" t="s">
+        <v>367</v>
       </c>
       <c r="N257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O257" s="2">
-        <v>209.70851999999999</v>
+        <v>200.62246999999999</v>
       </c>
       <c r="P257" s="2">
-        <v>198.52690999999999</v>
+        <v>195.100988</v>
       </c>
       <c r="Q257" t="s">
         <v>367</v>
@@ -16387,7 +16389,7 @@
         <v>392</v>
       </c>
       <c r="B258" t="s">
-        <v>308</v>
+        <v>263</v>
       </c>
       <c r="C258">
         <v>7000</v>
@@ -16396,16 +16398,16 @@
         <v>300</v>
       </c>
       <c r="E258" s="1">
-        <v>1.4308599999999999E-3</v>
-      </c>
-      <c r="F258">
-        <v>356.18635999999998</v>
-      </c>
-      <c r="G258">
-        <v>352.94099999999997</v>
+        <v>1.5328200000000001E-3</v>
+      </c>
+      <c r="F258" s="7">
+        <v>354.48030999999997</v>
+      </c>
+      <c r="G258" s="7">
+        <v>353.61534999999998</v>
       </c>
       <c r="H258">
-        <v>352.20198399999998</v>
+        <v>352.773302</v>
       </c>
       <c r="I258" t="s">
         <v>367</v>
@@ -16413,11 +16415,11 @@
       <c r="J258">
         <v>0</v>
       </c>
-      <c r="K258">
-        <v>354.89026000000001</v>
-      </c>
-      <c r="L258">
-        <v>354.64640600000001</v>
+      <c r="K258" s="7">
+        <v>354.41550000000001</v>
+      </c>
+      <c r="L258" s="2">
+        <v>354.26106199999998</v>
       </c>
       <c r="M258" t="s">
         <v>367</v>
@@ -16426,10 +16428,10 @@
         <v>0</v>
       </c>
       <c r="O258" s="2">
-        <v>265.5181</v>
+        <v>257.99099000000001</v>
       </c>
       <c r="P258" s="2">
-        <v>262.12535600000001</v>
+        <v>247.200424</v>
       </c>
       <c r="Q258" t="s">
         <v>367</v>
@@ -16443,7 +16445,7 @@
         <v>392</v>
       </c>
       <c r="B259" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="C259">
         <v>7000</v>
@@ -16452,16 +16454,16 @@
         <v>400</v>
       </c>
       <c r="E259" s="1">
-        <v>1.4308599999999999E-3</v>
-      </c>
-      <c r="F259">
-        <v>447.37688000000003</v>
-      </c>
-      <c r="G259">
-        <v>444.83702</v>
+        <v>1.5328200000000001E-3</v>
+      </c>
+      <c r="F259" s="7">
+        <v>442.88303999999999</v>
+      </c>
+      <c r="G259" s="7">
+        <v>440.51258999999999</v>
       </c>
       <c r="H259">
-        <v>442.680902</v>
+        <v>439.09607399999999</v>
       </c>
       <c r="I259" t="s">
         <v>367</v>
@@ -16469,11 +16471,11 @@
       <c r="J259">
         <v>0</v>
       </c>
-      <c r="K259">
-        <v>446.34676999999999</v>
-      </c>
-      <c r="L259">
-        <v>446.04652199999998</v>
+      <c r="K259" s="7">
+        <v>442.50301000000002</v>
+      </c>
+      <c r="L259" s="2">
+        <v>442.09483599999999</v>
       </c>
       <c r="M259" t="s">
         <v>367</v>
@@ -16482,10 +16484,10 @@
         <v>0</v>
       </c>
       <c r="O259" s="2">
-        <v>328.1669</v>
+        <v>303.73565000000002</v>
       </c>
       <c r="P259" s="2">
-        <v>317.77804600000002</v>
+        <v>294.27895599999999</v>
       </c>
       <c r="Q259" t="s">
         <v>367</v>
@@ -16499,7 +16501,7 @@
         <v>392</v>
       </c>
       <c r="B260" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="C260">
         <v>7000</v>
@@ -16508,16 +16510,16 @@
         <v>500</v>
       </c>
       <c r="E260" s="1">
-        <v>1.4308599999999999E-3</v>
-      </c>
-      <c r="F260">
-        <v>533.21672000000001</v>
-      </c>
-      <c r="G260">
-        <v>530.67209000000003</v>
+        <v>1.5328200000000001E-3</v>
+      </c>
+      <c r="F260" s="7">
+        <v>524.14255000000003</v>
+      </c>
+      <c r="G260" s="7">
+        <v>521.37064999999996</v>
       </c>
       <c r="H260">
-        <v>529.58963400000005</v>
+        <v>520.72209799999996</v>
       </c>
       <c r="I260" t="s">
         <v>367</v>
@@ -16525,11 +16527,11 @@
       <c r="J260">
         <v>0</v>
       </c>
-      <c r="K260">
-        <v>532.37554</v>
-      </c>
-      <c r="L260">
-        <v>532.15853200000004</v>
+      <c r="K260" s="7">
+        <v>523.64688999999998</v>
+      </c>
+      <c r="L260" s="2">
+        <v>523.14608399999997</v>
       </c>
       <c r="M260" t="s">
         <v>367</v>
@@ -16538,10 +16540,10 @@
         <v>0</v>
       </c>
       <c r="O260" s="2">
-        <v>381.12632000000002</v>
+        <v>375.50416999999999</v>
       </c>
       <c r="P260" s="2">
-        <v>372.77113000000003</v>
+        <v>364.401656</v>
       </c>
       <c r="Q260" t="s">
         <v>367</v>
@@ -16561,39 +16563,39 @@
       <c r="D261" s="8"/>
       <c r="E261" s="9"/>
       <c r="F261" s="8"/>
-      <c r="G261" s="8">
+      <c r="G261" s="12">
         <f t="array" ref="G261">AVERAGE((F211:F260-G211:G260)/F211:F260)</f>
-        <v>2.6214849643415423E-3</v>
-      </c>
-      <c r="H261" s="8">
+        <v>2.6957450207992727E-3</v>
+      </c>
+      <c r="H261" s="12">
         <f t="array" ref="H261">AVERAGE((F211:F260-H211:H260)/F211:F260)</f>
-        <v>4.8701247413402617E-3</v>
+        <v>4.6414921834512816E-3</v>
       </c>
       <c r="I261" s="8"/>
       <c r="J261" s="8">
         <f>SUM(J211:J260)</f>
-        <v>19</v>
-      </c>
-      <c r="K261" s="8">
+        <v>27</v>
+      </c>
+      <c r="K261" s="12">
         <f t="array" ref="K261">AVERAGE((F211:F260-K211:K260)/F211:F260)</f>
-        <v>6.3619381944724342E-4</v>
-      </c>
-      <c r="L261" s="8">
+        <v>5.7301525945369601E-4</v>
+      </c>
+      <c r="L261" s="12">
         <f t="array" ref="L261">AVERAGE((F211:F260-L211:L260)/F211:F260)</f>
-        <v>1.0789381756105482E-3</v>
+        <v>9.6979604099909082E-4</v>
       </c>
       <c r="M261" s="8"/>
       <c r="N261" s="8">
         <f>SUM(N211:N260)</f>
-        <v>72</v>
-      </c>
-      <c r="O261" s="10">
+        <v>77</v>
+      </c>
+      <c r="O261" s="12">
         <f t="array" ref="O261">AVERAGE((F211:F260-O211:O260)/F211:F260)</f>
-        <v>0.2526580074031784</v>
-      </c>
-      <c r="P261" s="10">
+        <v>0.25265676572008156</v>
+      </c>
+      <c r="P261" s="12">
         <f t="array" ref="P261">AVERAGE((F211:F260-P211:P260)/F211:F260)</f>
-        <v>0.28801244013039012</v>
+        <v>0.28795986062188328</v>
       </c>
       <c r="Q261" s="8"/>
       <c r="R261" s="8">
@@ -16747,7 +16749,7 @@
       <c r="K264">
         <v>322.22865999999999</v>
       </c>
-      <c r="L264">
+      <c r="L264" s="16">
         <v>321.97440599999999</v>
       </c>
       <c r="M264" t="s">
@@ -16791,8 +16793,8 @@
       <c r="G265">
         <v>392.06358999999998</v>
       </c>
-      <c r="H265">
-        <v>390.24020400000001</v>
+      <c r="H265" s="16">
+        <v>390.38539200000002</v>
       </c>
       <c r="I265" t="s">
         <v>367</v>
@@ -16803,8 +16805,8 @@
       <c r="K265">
         <v>393.96911</v>
       </c>
-      <c r="L265">
-        <v>393.54638999999997</v>
+      <c r="L265" s="16">
+        <v>393.52470799999998</v>
       </c>
       <c r="M265" t="s">
         <v>367</v>
@@ -16812,11 +16814,11 @@
       <c r="N265">
         <v>0</v>
       </c>
-      <c r="O265" s="7">
+      <c r="O265" s="19">
         <v>290.55641000000003</v>
       </c>
-      <c r="P265" s="2">
-        <v>268.12577800000003</v>
+      <c r="P265" s="18">
+        <v>261.67109399999998</v>
       </c>
       <c r="Q265" t="s">
         <v>367</v>
@@ -16892,39 +16894,39 @@
       <c r="D267" s="8"/>
       <c r="E267" s="9"/>
       <c r="F267" s="8"/>
-      <c r="G267" s="8">
+      <c r="G267" s="12">
         <f t="array" ref="G267">AVERAGE((F262:F266-G262:G266)/F262:F266)</f>
         <v>8.2269103605319936E-3</v>
       </c>
-      <c r="H267" s="8">
+      <c r="H267" s="12">
         <f t="array" ref="H267">AVERAGE((F262:F266-H262:H266)/F262:F266)</f>
-        <v>1.1735767919018673E-2</v>
+        <v>1.1662644494456319E-2</v>
       </c>
       <c r="I267" s="8"/>
       <c r="J267" s="8">
         <f>SUM(J262:J266)</f>
         <v>0</v>
       </c>
-      <c r="K267" s="8">
+      <c r="K267" s="12">
         <f t="array" ref="K267">AVERAGE((F262:F266-K262:K266)/F262:F266)</f>
         <v>4.0773277962307302E-3</v>
       </c>
-      <c r="L267" s="8">
+      <c r="L267" s="12">
         <f t="array" ref="L267">AVERAGE((F262:F266-L262:L266)/F262:F266)</f>
-        <v>4.7196465190507729E-3</v>
+        <v>4.7305665819441295E-3</v>
       </c>
       <c r="M267" s="8"/>
       <c r="N267" s="8">
         <f>SUM(N262:N266)</f>
         <v>0</v>
       </c>
-      <c r="O267" s="10">
+      <c r="O267" s="12">
         <f t="array" ref="O267">AVERAGE((F262:F266-O262:O266)/F262:F266)</f>
         <v>0.31017737032213855</v>
       </c>
-      <c r="P267" s="10">
+      <c r="P267" s="12">
         <f t="array" ref="P267">AVERAGE((F262:F266-P262:P266)/F262:F266)</f>
-        <v>0.34303704753430464</v>
+        <v>0.34628792638481415</v>
       </c>
       <c r="Q267" s="8"/>
       <c r="R267" s="8">
@@ -19410,11 +19412,11 @@
       <c r="D313" s="8"/>
       <c r="E313" s="9"/>
       <c r="F313" s="8"/>
-      <c r="G313" s="8">
+      <c r="G313" s="17">
         <f t="array" ref="G313">AVERAGE((F276:F312-G276:G312)/F276:F312)</f>
         <v>2.4267485684229956E-3</v>
       </c>
-      <c r="H313" s="8">
+      <c r="H313" s="17">
         <f t="array" ref="H313">AVERAGE((F276:F312-H276:H312)/F276:F312)</f>
         <v>2.5739789420904085E-3</v>
       </c>
@@ -19423,11 +19425,11 @@
         <f>SUM(J276:J312)</f>
         <v>135</v>
       </c>
-      <c r="K313" s="8">
+      <c r="K313" s="17">
         <f t="array" ref="K313">AVERAGE((F276:F312-K276:K312)/F276:F312)</f>
         <v>2.2448027740352059E-3</v>
       </c>
-      <c r="L313" s="8">
+      <c r="L313" s="17">
         <f t="array" ref="L313">AVERAGE((F276:F312-L276:L312)/F276:F312)</f>
         <v>2.3605553781793618E-3</v>
       </c>
@@ -19436,11 +19438,11 @@
         <f>SUM(N276:N312)</f>
         <v>142</v>
       </c>
-      <c r="O313" s="10">
+      <c r="O313" s="17">
         <f t="array" ref="O313">AVERAGE((F276:F312-O276:O312)/F276:F312)</f>
         <v>2.5001749433333355E-3</v>
       </c>
-      <c r="P313" s="10">
+      <c r="P313" s="17">
         <f t="array" ref="P313">AVERAGE((F276:F312-P276:P312)/F276:F312)</f>
         <v>2.7633878534528387E-3</v>
       </c>
@@ -21755,11 +21757,11 @@
       <c r="D355" s="8"/>
       <c r="E355" s="9"/>
       <c r="F355" s="8"/>
-      <c r="G355" s="8">
+      <c r="G355" s="17">
         <f t="array" ref="G355">AVERAGE((F314:F354-G314:G354)/F314:F354)</f>
         <v>5.293460713895517E-4</v>
       </c>
-      <c r="H355" s="8">
+      <c r="H355" s="17">
         <f t="array" ref="H355">AVERAGE((F314:F354-H314:H354)/F314:F354)</f>
         <v>8.6166575562223987E-4</v>
       </c>
@@ -21768,11 +21770,11 @@
         <f>SUM(J314:J354)</f>
         <v>68</v>
       </c>
-      <c r="K355" s="8">
+      <c r="K355" s="17">
         <f t="array" ref="K355">AVERAGE((F314:F354-K314:K354)/F314:F354)</f>
         <v>2.0132481772161531E-4</v>
       </c>
-      <c r="L355" s="8">
+      <c r="L355" s="17">
         <f t="array" ref="L355">AVERAGE((F314:F354-L314:L354)/F314:F354)</f>
         <v>4.3650180524949154E-4</v>
       </c>
@@ -21781,11 +21783,11 @@
         <f>SUM(N314:N354)</f>
         <v>111</v>
       </c>
-      <c r="O355" s="10">
+      <c r="O355" s="17">
         <f t="array" ref="O355">AVERAGE((F314:F354-O314:O354)/F314:F354)</f>
         <v>1.1826429680795736E-3</v>
       </c>
-      <c r="P355" s="10">
+      <c r="P355" s="17">
         <f t="array" ref="P355">AVERAGE((F314:F354-P314:P354)/F314:F354)</f>
         <v>1.648301477585325E-3</v>
       </c>
@@ -22035,10 +22037,10 @@
         <v>130</v>
       </c>
       <c r="G361">
-        <v>148</v>
+        <v>422</v>
       </c>
       <c r="H361">
-        <v>260.60000000000002</v>
+        <v>565.20000000000005</v>
       </c>
       <c r="I361" t="s">
         <v>367</v>
@@ -22050,13 +22052,13 @@
         <v>130</v>
       </c>
       <c r="L361">
-        <v>153.80000000000001</v>
+        <v>130</v>
       </c>
       <c r="M361" s="5">
-        <v>11.322127</v>
+        <v>19.501142000000002</v>
       </c>
       <c r="N361">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.3">
